--- a/docs/oc-top-proveedores/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-proveedores/licencia-de-software-de-ofimatica.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="licencia-de-soft top prov" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="licencia-de-soft top prov" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -18002,7 +18002,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18444,7 +18444,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20892,7 +20892,7 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22894,7 +22894,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24911,7 +24911,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -25662,7 +25662,7 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -25834,7 +25834,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -26017,7 +26017,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -26261,7 +26261,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26505,7 +26505,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26688,7 +26688,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26886,7 +26886,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26997,7 +26997,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -27241,7 +27241,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27729,7 +27729,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28583,7 +28583,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28766,7 +28766,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28842,7 +28842,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -28953,7 +28953,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -29136,7 +29136,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29197,7 +29197,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29273,7 +29273,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -29384,7 +29384,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29811,7 +29811,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -30055,7 +30055,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30070,7 +30070,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -30547,7 +30547,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30852,7 +30852,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -31035,7 +31035,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -31401,7 +31401,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31645,7 +31645,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -32743,7 +32743,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -33063,7 +33063,7 @@
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -34577,7 +34577,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34882,7 +34882,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -35126,7 +35126,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35187,7 +35187,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35248,7 +35248,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35736,7 +35736,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35797,7 +35797,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -36163,7 +36163,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36666,7 +36666,7 @@
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="K597" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37772,7 +37772,7 @@
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
@@ -37837,7 +37837,7 @@
       </c>
       <c r="K611" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
@@ -37902,7 +37902,7 @@
       </c>
       <c r="K612" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
@@ -39111,7 +39111,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39172,7 +39172,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39904,7 +39904,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39980,7 +39980,7 @@
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -40106,7 +40106,7 @@
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
@@ -40217,7 +40217,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40720,7 +40720,7 @@
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
@@ -40953,7 +40953,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -41136,7 +41136,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41395,7 +41395,7 @@
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L669" t="inlineStr">
@@ -41445,7 +41445,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41628,7 +41628,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41689,7 +41689,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41811,7 +41811,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41872,7 +41872,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41887,7 +41887,7 @@
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L677" t="inlineStr">
@@ -41937,7 +41937,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41998,7 +41998,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -42120,7 +42120,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42181,7 +42181,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42242,7 +42242,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42303,7 +42303,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42364,7 +42364,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42425,7 +42425,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42486,7 +42486,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42547,7 +42547,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42608,7 +42608,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42669,7 +42669,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42730,7 +42730,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42791,7 +42791,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42852,7 +42852,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42913,7 +42913,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42974,7 +42974,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -43035,7 +43035,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -43096,7 +43096,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43218,7 +43218,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43279,7 +43279,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43340,7 +43340,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43523,7 +43523,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43584,7 +43584,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43645,7 +43645,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43767,7 +43767,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43828,7 +43828,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43889,7 +43889,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43950,7 +43950,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -44011,7 +44011,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44072,7 +44072,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -44133,7 +44133,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44194,7 +44194,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44255,7 +44255,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44316,7 +44316,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44377,7 +44377,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44438,7 +44438,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
@@ -44503,7 +44503,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44579,7 +44579,7 @@
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
@@ -44629,7 +44629,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44690,7 +44690,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">

--- a/docs/oc-top-proveedores/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-proveedores/licencia-de-software-de-ofimatica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M768"/>
+  <dimension ref="A1:M770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15611,7 +15611,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1020-311-CM25</t>
+          <t>4555-190-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15636,43 +15636,47 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>414234.24</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4555-190-CM25</t>
+          <t>1020-311-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15697,41 +15701,37 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>10652.88</v>
+        <v>414234.24</v>
       </c>
     </row>
     <row r="237">
@@ -16448,7 +16448,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2429-2562-CM25</t>
+          <t>688-173-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16468,32 +16468,32 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -16507,13 +16507,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>8205.219999999999</v>
+        <v>71582.07000000001</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>688-173-CM25</t>
+          <t>2429-2562-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16533,32 +16533,32 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -16572,7 +16572,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>71582.07000000001</v>
+        <v>8205.219999999999</v>
       </c>
     </row>
     <row r="250">
@@ -16643,7 +16643,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>618923-218-CM25</t>
+          <t>752-374-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16663,48 +16663,52 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.979.970-4</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>185452.93</v>
+        <v>36945.22</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>752-374-CM25</t>
+          <t>797305-87-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16724,32 +16728,32 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -16763,13 +16767,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>36945.22</v>
+        <v>75963.64999999999</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>797305-87-CM25</t>
+          <t>618923-218-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16794,12 +16798,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>61.979.970-4</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16809,32 +16813,28 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>75963.64999999999</v>
+        <v>185452.93</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2409-1257-CM25</t>
+          <t>3756-627-CM25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16854,32 +16854,32 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16893,13 +16893,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>22193.5</v>
+        <v>11584.65</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3756-627-CM25</t>
+          <t>2409-1257-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16919,32 +16919,32 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -16958,7 +16958,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>11584.65</v>
+        <v>22193.5</v>
       </c>
     </row>
     <row r="256">
@@ -17935,7 +17935,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3863-347-CM25</t>
+          <t>2594-926-CM25</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17955,37 +17955,37 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -17994,13 +17994,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1480.57</v>
+        <v>5286.87</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2408-4495-CM25</t>
+          <t>4455-765-CM25</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18025,12 +18025,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -18040,17 +18040,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -18059,13 +18059,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1903.27</v>
+        <v>845.9</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1057931-109-CM25</t>
+          <t>2408-4495-CM25</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18090,12 +18090,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -18105,17 +18105,17 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -18124,13 +18124,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>10150.8</v>
+        <v>1903.27</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2594-926-CM25</t>
+          <t>3863-347-CM25</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18150,37 +18150,37 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -18189,13 +18189,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>5286.87</v>
+        <v>1480.57</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4455-765-CM25</t>
+          <t>1057931-109-CM25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18220,12 +18220,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18254,7 +18254,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>845.9</v>
+        <v>10150.8</v>
       </c>
     </row>
     <row r="276">
@@ -18325,7 +18325,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2906-217-CM25</t>
+          <t>1055513-3-CM25</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18350,27 +18350,27 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -18384,13 +18384,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>26632.2</v>
+        <v>2749.17</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1055513-3-CM25</t>
+          <t>2906-217-CM25</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18415,27 +18415,27 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2749.17</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="279">
@@ -18910,7 +18910,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>4928-100-CM25</t>
+          <t>3863-431-CM25</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18935,17 +18935,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>3806.33</v>
+        <v>3806.55</v>
       </c>
     </row>
     <row r="287">
@@ -19040,7 +19040,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>3863-431-CM25</t>
+          <t>4928-100-CM25</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19065,17 +19065,17 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -19099,7 +19099,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3806.55</v>
+        <v>3806.33</v>
       </c>
     </row>
     <row r="289">
@@ -19300,7 +19300,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1076403-37-CM25</t>
+          <t>1607-191-CM25</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19340,12 +19340,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -19359,13 +19359,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>891357.6</v>
+        <v>53878.44</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>4497-51-CM25</t>
+          <t>1182705-225-CM25</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19390,17 +19390,17 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.073.100-2</t>
+          <t>65.199.131-5</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>10573.15</v>
+        <v>33834.08</v>
       </c>
     </row>
     <row r="294">
@@ -19495,7 +19495,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1607-191-CM25</t>
+          <t>4497-51-CM25</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19520,12 +19520,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.073.100-2</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19535,12 +19535,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -19554,13 +19554,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>53878.44</v>
+        <v>10573.15</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1182705-225-CM25</t>
+          <t>1076403-37-CM25</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19585,27 +19585,27 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>65.199.131-5</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -19619,7 +19619,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>33834.08</v>
+        <v>891357.6</v>
       </c>
     </row>
     <row r="297">
@@ -20015,7 +20015,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4455-854-CM25</t>
+          <t>628-339-CM25</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20040,32 +20040,32 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -20074,13 +20074,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>5498.04</v>
+        <v>82419.39999999999</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>623663-460-CM25</t>
+          <t>4455-854-CM25</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20100,37 +20100,37 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>65.030.848-4</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -20139,13 +20139,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>36945.22</v>
+        <v>5498.04</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>628-339-CM25</t>
+          <t>623663-460-CM25</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20165,17 +20165,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>65.030.848-4</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20185,12 +20185,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -20204,7 +20204,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>82419.39999999999</v>
+        <v>36945.22</v>
       </c>
     </row>
     <row r="306">
@@ -20336,7 +20336,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>14-576-CM25</t>
+          <t>4455-877-CM25</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20361,32 +20361,32 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -20395,13 +20395,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>62653.5</v>
+        <v>2326.09</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>4455-877-CM25</t>
+          <t>14-576-CM25</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20426,32 +20426,32 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -20460,7 +20460,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2326.09</v>
+        <v>62653.5</v>
       </c>
     </row>
     <row r="310">
@@ -20718,7 +20718,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1057501-24877-CM25</t>
+          <t>3231-464-CM25</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20738,48 +20738,52 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>67173.12</v>
+        <v>14164.33</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>557639-2121-CM25</t>
+          <t>2760-88-CM25</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20804,27 +20808,27 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -20838,13 +20842,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>13956.56</v>
+        <v>11803.61</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>608897-11250-CM25</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20869,12 +20873,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20903,13 +20907,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>9727.92</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2760-88-CM25</t>
+          <t>557639-2121-CM25</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20934,27 +20938,27 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -20968,13 +20972,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>11803.61</v>
+        <v>13956.56</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>3231-464-CM25</t>
+          <t>1057501-24877-CM25</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20994,52 +20998,48 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>14164.33</v>
+        <v>67173.12</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>608897-11250-CM25</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21064,12 +21064,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>4863.77</v>
+        <v>9727.92</v>
       </c>
     </row>
     <row r="320">
@@ -21299,7 +21299,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2389-710-CM25</t>
+          <t>979-2016-CM25</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21319,37 +21319,37 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -21358,13 +21358,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2537.56</v>
+        <v>52865.75</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1431214-26-CM25</t>
+          <t>5520-10754-CM25</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21389,27 +21389,27 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -21423,13 +21423,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>4229.26</v>
+        <v>5733.42</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>979-2016-CM25</t>
+          <t>2389-710-CM25</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21449,37 +21449,37 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -21488,13 +21488,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>52865.75</v>
+        <v>2537.56</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5520-10754-CM25</t>
+          <t>1431214-26-CM25</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21519,27 +21519,27 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -21553,13 +21553,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>5733.42</v>
+        <v>4229.26</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1020-454-CM25</t>
+          <t>1057500-626-CM25</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21579,17 +21579,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21599,32 +21599,28 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>245698.11</v>
+        <v>67173.12</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1028897-1614-CM25</t>
+          <t>1020-454-CM25</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21649,17 +21645,17 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -21683,13 +21679,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>28141.83</v>
+        <v>245698.11</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1057500-626-CM25</t>
+          <t>1028897-1614-CM25</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21709,42 +21705,46 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>67173.12</v>
+        <v>28141.83</v>
       </c>
     </row>
     <row r="330">
@@ -23952,7 +23952,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4144-166-CM25</t>
+          <t>2817-928-CM25</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23977,17 +23977,17 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -24011,7 +24011,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>6123.76</v>
+        <v>50745.29</v>
       </c>
     </row>
     <row r="365">
@@ -24082,7 +24082,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2817-928-CM25</t>
+          <t>4144-166-CM25</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24107,17 +24107,17 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -24141,13 +24141,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>50745.29</v>
+        <v>6123.76</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>3053-62-CM25</t>
+          <t>5416-1524-CM25</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24167,32 +24167,32 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
@@ -24206,7 +24206,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>26080.72</v>
+        <v>1691.61</v>
       </c>
     </row>
     <row r="368">
@@ -24277,7 +24277,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5416-1524-CM25</t>
+          <t>3053-62-CM25</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24297,32 +24297,32 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
@@ -24336,7 +24336,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1691.61</v>
+        <v>26080.72</v>
       </c>
     </row>
     <row r="370">
@@ -24862,7 +24862,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>14-654-CM25</t>
+          <t>937232-1136-CM25</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24887,12 +24887,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -24902,12 +24902,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>22357.24</v>
+        <v>92320.2</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>937232-1136-CM25</t>
+          <t>14-654-CM25</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24952,12 +24952,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -24967,12 +24967,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -24986,7 +24986,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>92320.2</v>
+        <v>22357.24</v>
       </c>
     </row>
     <row r="380">
@@ -25707,7 +25707,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2674-1249-CM25</t>
+          <t>2777-925-CM25</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25727,32 +25727,32 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -25766,13 +25766,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>3171.77</v>
+        <v>49673.46</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2777-925-CM25</t>
+          <t>605-503-CM25</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25792,22 +25792,22 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.006.000-5</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -25831,13 +25831,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>49673.46</v>
+        <v>16779</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>605-503-CM25</t>
+          <t>2674-1249-CM25</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25862,12 +25862,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.006.000-5</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Consejo de Defensa del Estado</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25877,12 +25877,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -25896,7 +25896,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>16779</v>
+        <v>3171.77</v>
       </c>
     </row>
     <row r="394">
@@ -29997,7 +29997,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>4401-124-CM26</t>
+          <t>2934-12-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -30017,32 +30017,32 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
@@ -30056,13 +30056,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2875.98</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2934-12-CM26</t>
+          <t>4401-124-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -30082,32 +30082,32 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
@@ -30121,7 +30121,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>4435.13</v>
+        <v>2875.98</v>
       </c>
     </row>
     <row r="459">
@@ -30517,7 +30517,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>4052-22-CM26</t>
+          <t>2912-80-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30537,22 +30537,22 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -30576,13 +30576,13 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>10000.58</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2912-80-CM26</t>
+          <t>4052-22-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30602,22 +30602,22 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -30641,7 +30641,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>4435.13</v>
+        <v>10000.58</v>
       </c>
     </row>
     <row r="467">
@@ -30712,7 +30712,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>568658-365-CM26</t>
+          <t>1238177-14-CM26</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -30737,27 +30737,27 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -30771,13 +30771,13 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>30771.02</v>
+        <v>3534.3</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>1238177-14-CM26</t>
+          <t>539119-470-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -30802,12 +30802,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -30817,12 +30817,12 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
@@ -30836,13 +30836,13 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>3534.3</v>
+        <v>1056.9</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>539119-470-CM26</t>
+          <t>568658-365-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30867,27 +30867,27 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
@@ -30901,7 +30901,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1056.9</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="471">
@@ -31492,7 +31492,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2273-76-CM26</t>
+          <t>4766-3405-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -31512,37 +31512,37 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -31551,13 +31551,13 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>1479.66</v>
+        <v>13305.39</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>4766-3405-CM26</t>
+          <t>2273-76-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -31577,46 +31577,46 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I481" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J481" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K481" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>13305.39</v>
+        <v>1479.66</v>
       </c>
     </row>
     <row r="482">
@@ -32467,7 +32467,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>4127-129-CM26</t>
+          <t>1026727-66-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -32492,27 +32492,27 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
@@ -32526,13 +32526,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>36115.55</v>
+        <v>3827.04</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1026727-66-CM26</t>
+          <t>4127-129-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32557,27 +32557,27 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
@@ -32591,13 +32591,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>3827.04</v>
+        <v>36115.55</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>4252-84-CM26</t>
+          <t>5768-44-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32617,32 +32617,32 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -32656,13 +32656,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>9491.18</v>
+        <v>37485</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>4256-78-CM26</t>
+          <t>4732-64-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32682,22 +32682,22 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -32721,13 +32721,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>2661.08</v>
+        <v>14192.42</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>5768-44-CM26</t>
+          <t>4252-84-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32747,32 +32747,32 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
@@ -32786,13 +32786,13 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>37485</v>
+        <v>9491.18</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>4732-64-CM26</t>
+          <t>4256-78-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32812,22 +32812,22 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -32851,7 +32851,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>14192.42</v>
+        <v>2661.08</v>
       </c>
     </row>
     <row r="501">
@@ -32987,7 +32987,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2275-3705-CM25</t>
+          <t>1456840-17-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -33012,43 +33012,47 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K503" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>80607.74000000001</v>
+        <v>1173.34</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1456840-17-CM26</t>
+          <t>2275-3705-CM25</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -33073,41 +33077,37 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K504" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1173.34</v>
+        <v>80607.74000000001</v>
       </c>
     </row>
     <row r="505">
@@ -33438,7 +33438,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>4777-274-CM26</t>
+          <t>722-27-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33458,22 +33458,22 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -33497,13 +33497,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>31045.91</v>
+        <v>30742.22</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>722-27-CM26</t>
+          <t>4777-274-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33523,22 +33523,22 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -33562,7 +33562,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>30742.22</v>
+        <v>31045.91</v>
       </c>
     </row>
     <row r="512">
@@ -33828,7 +33828,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>3707-206-CM26</t>
+          <t>2410-54-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33853,47 +33853,43 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K516" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>13393.95</v>
+        <v>72770.88</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2410-54-CM26</t>
+          <t>4928-21-CM26</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -33918,43 +33914,47 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K517" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>72770.88</v>
+        <v>11412.58</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>4928-21-CM26</t>
+          <t>3707-206-CM26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -33979,27 +33979,27 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
@@ -34013,7 +34013,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>11412.58</v>
+        <v>13393.95</v>
       </c>
     </row>
     <row r="519">
@@ -34080,7 +34080,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>3621-125-CM26</t>
+          <t>2427-295-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -34100,17 +34100,17 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -34120,12 +34120,12 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
@@ -34139,13 +34139,13 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>17387.27</v>
+        <v>13205.43</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2427-295-CM26</t>
+          <t>3621-125-CM26</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -34165,17 +34165,17 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -34185,12 +34185,12 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -34204,7 +34204,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>13205.43</v>
+        <v>17387.27</v>
       </c>
     </row>
     <row r="522">
@@ -34860,7 +34860,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>4294-60-CM26</t>
+          <t>1216088-95-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -34885,12 +34885,12 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>65.077.010-2</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -34900,17 +34900,17 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -34919,13 +34919,13 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>14794.08</v>
+        <v>845.38</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>1216088-95-CM26</t>
+          <t>542429-19-CM26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -34950,17 +34950,17 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -34984,13 +34984,13 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>845.38</v>
+        <v>7890.56</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>542429-19-CM26</t>
+          <t>4294-60-CM26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -35015,32 +35015,32 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>65.077.010-2</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -35049,7 +35049,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>7890.56</v>
+        <v>14794.08</v>
       </c>
     </row>
     <row r="535">
@@ -35120,7 +35120,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>3712-291-CM26</t>
+          <t>4454-332-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -35140,32 +35140,32 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
@@ -35179,13 +35179,13 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>11718.64</v>
+        <v>2307.83</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>4454-332-CM26</t>
+          <t>3712-291-CM26</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -35205,32 +35205,32 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
@@ -35244,7 +35244,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>2307.83</v>
+        <v>11718.64</v>
       </c>
     </row>
     <row r="538">
@@ -36095,7 +36095,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>3157-25-CM26</t>
+          <t>699360-19-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -36120,27 +36120,27 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
@@ -36154,13 +36154,13 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>1951.46</v>
+        <v>4325.59</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>699360-19-CM26</t>
+          <t>3157-25-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -36185,27 +36185,27 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
@@ -36219,7 +36219,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>4325.59</v>
+        <v>1951.46</v>
       </c>
     </row>
     <row r="553">
@@ -37196,7 +37196,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>4238-132-CM26</t>
+          <t>2069-4322-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -37221,27 +37221,27 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
@@ -37255,13 +37255,13 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>19514.57</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2069-4322-CM26</t>
+          <t>4238-132-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -37286,27 +37286,27 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
@@ -37320,7 +37320,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>1031.66</v>
+        <v>19514.57</v>
       </c>
     </row>
     <row r="570">
@@ -39268,7 +39268,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>3553-166-CM26</t>
+          <t>750998-67-CM26</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -39288,17 +39288,17 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.255.100-1</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -39327,13 +39327,13 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>196849.99</v>
+        <v>10567.2</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>750998-67-CM26</t>
+          <t>3553-166-CM26</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -39353,17 +39353,17 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>69.255.100-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -39392,7 +39392,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>10567.2</v>
+        <v>196849.99</v>
       </c>
     </row>
     <row r="602">
@@ -40503,7 +40503,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>1368-34-CM26</t>
+          <t>3921-323-CM26</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -40528,17 +40528,17 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -40562,7 +40562,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>10769.86</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="620">
@@ -41019,7 +41019,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>5586-2119-CM26</t>
+          <t>1368-34-CM26</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -41044,27 +41044,27 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
@@ -41078,13 +41078,13 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>62229.5</v>
+        <v>10769.86</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>3921-323-CM26</t>
+          <t>5586-2119-CM26</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -41109,12 +41109,12 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -41124,12 +41124,12 @@
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
@@ -41143,7 +41143,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>22175.65</v>
+        <v>62229.5</v>
       </c>
     </row>
     <row r="629">
@@ -41539,7 +41539,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2021-131-CM26</t>
+          <t>975-207-CM26</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -41564,12 +41564,12 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -41598,13 +41598,13 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>21044.51</v>
+        <v>1375.54</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>1609-221-CM26</t>
+          <t>2021-131-CM26</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -41629,17 +41629,17 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -41663,13 +41663,13 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>12405.21</v>
+        <v>21044.51</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>1609-221-CM26</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -41694,17 +41694,17 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -41728,7 +41728,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1375.54</v>
+        <v>12405.21</v>
       </c>
     </row>
     <row r="638">
@@ -41994,7 +41994,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>4077-104-CM26</t>
+          <t>539119-2289-CM26</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -42019,7 +42019,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -42029,37 +42029,37 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I642" t="inlineStr">
-        <is>
-          <t>COMPUTACION INTEGRAL S A</t>
-        </is>
-      </c>
-      <c r="J642" t="inlineStr">
-        <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K642" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>6761.87</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>699360-38-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -42084,27 +42084,27 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
@@ -42118,13 +42118,13 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>887.03</v>
+        <v>4587.2</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>699360-38-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -42149,27 +42149,27 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
@@ -42183,13 +42183,13 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>4587.2</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>4077-104-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -42209,37 +42209,37 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
@@ -42248,13 +42248,13 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>1031.66</v>
+        <v>6761.87</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>539119-2289-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -42274,37 +42274,37 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -42313,7 +42313,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>845.23</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="647">
@@ -42705,7 +42705,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>3073-290-CM26</t>
+          <t>2582-255-SE26</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -42730,27 +42730,27 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
@@ -42764,13 +42764,13 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>5226.19</v>
+        <v>218562.54</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2582-255-SE26</t>
+          <t>3073-290-CM26</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -42795,27 +42795,27 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -42829,7 +42829,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>218562.54</v>
+        <v>5226.19</v>
       </c>
     </row>
     <row r="655">
@@ -43745,7 +43745,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>3692-270-CM26</t>
+          <t>3996-373-CM26</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -43770,17 +43770,17 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -43804,13 +43804,13 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>7717.13</v>
+        <v>7983.23</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>3996-373-CM26</t>
+          <t>3692-270-CM26</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -43835,17 +43835,17 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -43869,7 +43869,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>7983.23</v>
+        <v>7717.13</v>
       </c>
     </row>
     <row r="671">
@@ -44655,7 +44655,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2732-21-CM26</t>
+          <t>3084-121-CM26</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -44675,32 +44675,32 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
@@ -44714,13 +44714,13 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>165430.94</v>
+        <v>77339.91</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>3084-121-CM26</t>
+          <t>1606-281-CM26</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -44745,27 +44745,27 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
@@ -44779,13 +44779,13 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>77339.91</v>
+        <v>6082.09</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>1606-281-CM26</t>
+          <t>1750-263-CM26</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -44810,12 +44810,12 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -44825,12 +44825,12 @@
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
@@ -44844,13 +44844,13 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>6082.09</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>3690-213-CM26</t>
+          <t>2732-21-CM26</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -44875,27 +44875,27 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
@@ -44909,13 +44909,13 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>14779.8</v>
+        <v>165430.94</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>1750-263-CM26</t>
+          <t>3690-213-CM26</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -44935,32 +44935,32 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
@@ -44974,7 +44974,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>10644.31</v>
+        <v>14779.8</v>
       </c>
     </row>
     <row r="688">
@@ -45695,7 +45695,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>1237849-145-CM26</t>
+          <t>3997-306-CM26</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -45715,22 +45715,22 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>65.081.056-2</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -45754,7 +45754,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>3077.1</v>
+        <v>14635.93</v>
       </c>
     </row>
     <row r="700">
@@ -45825,7 +45825,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>3997-306-CM26</t>
+          <t>4177-92-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -45850,27 +45850,27 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
@@ -45884,13 +45884,13 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>14635.93</v>
+        <v>8769.74</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>4177-92-CM26</t>
+          <t>1237849-145-CM26</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -45910,32 +45910,32 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>65.081.056-2</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K702" t="inlineStr">
@@ -45949,7 +45949,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>8769.74</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="703">
@@ -46800,7 +46800,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>688-100-CM26</t>
+          <t>1375746-102-CM26</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -46820,17 +46820,17 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -46840,12 +46840,12 @@
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
@@ -46859,13 +46859,13 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>71574.92999999999</v>
+        <v>16260.16</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>1375746-102-CM26</t>
+          <t>688-100-CM26</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -46885,17 +46885,17 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -46905,12 +46905,12 @@
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
@@ -46924,7 +46924,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>16260.16</v>
+        <v>71574.92999999999</v>
       </c>
     </row>
     <row r="718">
@@ -47645,7 +47645,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>5066-202-CM26</t>
+          <t>1260-126-SE26</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -47665,37 +47665,37 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Extranjero</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
@@ -47704,13 +47704,13 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>17475.15</v>
+        <v>106407.42</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>1175-708-CM26</t>
+          <t>5066-202-CM26</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -47725,22 +47725,22 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -47750,12 +47750,12 @@
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
@@ -47769,7 +47769,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>132839.7</v>
+        <v>17475.15</v>
       </c>
     </row>
     <row r="731">
@@ -47840,7 +47840,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>858-348-SE26</t>
+          <t>1175-708-CM26</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -47865,17 +47865,17 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -47899,13 +47899,13 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>713286</v>
+        <v>132839.7</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>867990-485-CM26</t>
+          <t>858-348-SE26</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -47925,17 +47925,17 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -47945,12 +47945,12 @@
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
@@ -47964,13 +47964,13 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>224910</v>
+        <v>713286</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>4414-1161-CM26</t>
+          <t>867990-485-CM26</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -47995,27 +47995,27 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
@@ -48029,7 +48029,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>29687.88</v>
+        <v>224910</v>
       </c>
     </row>
     <row r="735">
@@ -48100,7 +48100,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>2412-528-CM26</t>
+          <t>4414-1161-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -48110,47 +48110,47 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
@@ -48159,13 +48159,13 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>10565.42</v>
+        <v>29687.88</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2799-897-CM26</t>
+          <t>2412-528-CM26</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -48180,57 +48180,57 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I737" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J737" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K737" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>218446.87</v>
+        <v>10565.42</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>604944-108-CM26</t>
+          <t>2799-897-CM26</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -48255,27 +48255,27 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
@@ -48289,13 +48289,13 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>8388.07</v>
+        <v>218446.87</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2733-421-CM26</t>
+          <t>604944-108-CM26</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -48310,7 +48310,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -48320,12 +48320,12 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -48335,17 +48335,17 @@
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L739" t="inlineStr">
@@ -48354,13 +48354,13 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>6339.25</v>
+        <v>8388.07</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2389-523-CM26</t>
+          <t>2733-421-CM26</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -48385,32 +48385,32 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L740" t="inlineStr">
@@ -48419,13 +48419,13 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>5111.76</v>
+        <v>6339.25</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2429-1124-CM26</t>
+          <t>2389-523-CM26</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -48440,37 +48440,37 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
@@ -48484,13 +48484,13 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>35154.5</v>
+        <v>5111.76</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>3696-241-CM26</t>
+          <t>2429-1124-CM26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -48505,37 +48505,37 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
@@ -48549,13 +48549,13 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>8923.6</v>
+        <v>35154.5</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>3880-448-CM26</t>
+          <t>3696-241-CM26</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -48580,12 +48580,12 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -48614,13 +48614,13 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>26610.78</v>
+        <v>8923.6</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>595636-75-CM26</t>
+          <t>3880-448-CM26</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -48645,17 +48645,17 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -48679,13 +48679,13 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>62978.85</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>1080157-134-CM26</t>
+          <t>595636-75-CM26</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -48700,42 +48700,42 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L745" t="inlineStr">
@@ -48744,7 +48744,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>2747.01</v>
+        <v>62978.85</v>
       </c>
     </row>
     <row r="746">
@@ -48880,7 +48880,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>1049-1453-CM26</t>
+          <t>1080157-134-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -48900,17 +48900,17 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>61.310.000-8</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>INSTITUTO DE FOMENTO PESQUERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -48920,17 +48920,17 @@
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L748" t="inlineStr">
@@ -48939,7 +48939,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>2579.15</v>
+        <v>2747.01</v>
       </c>
     </row>
     <row r="749">
@@ -49010,7 +49010,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2305-63-CM26</t>
+          <t>1049-1453-CM26</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -49025,27 +49025,27 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>61.310.000-8</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>INSTITUTO DE FOMENTO PESQUERO</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -49069,13 +49069,13 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>5158.29</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>4728-326-CM26</t>
+          <t>2305-63-CM26</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -49100,17 +49100,17 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>60.719.000-3</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -49134,13 +49134,13 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>7221.61</v>
+        <v>5158.29</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>3695-420-CM26</t>
+          <t>4728-326-CM26</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -49165,27 +49165,27 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>60.719.000-3</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K752" t="inlineStr">
@@ -49199,13 +49199,13 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>923.13</v>
+        <v>7221.61</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2434-37-CM26</t>
+          <t>3695-420-CM26</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -49220,37 +49220,37 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K753" t="inlineStr">
@@ -49264,13 +49264,13 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>120303.05</v>
+        <v>923.13</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>979-1248-CM26</t>
+          <t>2434-37-CM26</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -49295,12 +49295,12 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -49310,12 +49310,12 @@
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
@@ -49329,13 +49329,13 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>28709.51</v>
+        <v>120303.05</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2981-1144-CM26</t>
+          <t>979-1248-CM26</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -49355,17 +49355,17 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -49394,13 +49394,13 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>5772.69</v>
+        <v>28709.51</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>619284-146-CM26</t>
+          <t>2981-1144-CM26</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -49415,22 +49415,22 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>61.980.000-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -49440,12 +49440,12 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
@@ -49459,13 +49459,13 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>2751.09</v>
+        <v>5772.69</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>1057448-421-CM26</t>
+          <t>619284-146-CM26</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -49490,17 +49490,17 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.980.000-1</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -49524,13 +49524,13 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>8979.690000000001</v>
+        <v>2751.09</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2906-131-CM26</t>
+          <t>1057448-421-CM26</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -49555,27 +49555,27 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
@@ -49589,13 +49589,13 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>26610.78</v>
+        <v>8979.690000000001</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>3674-585-CM26</t>
+          <t>2906-131-CM26</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -49620,27 +49620,27 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
@@ -49654,13 +49654,13 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>17577.25</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>872-572-CM26</t>
+          <t>3674-585-CM26</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -49675,37 +49675,37 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
@@ -49719,13 +49719,13 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>57068.83</v>
+        <v>17577.25</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>1533460-50-CM26</t>
+          <t>872-572-CM26</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -49740,22 +49740,22 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -49765,12 +49765,12 @@
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
@@ -49784,13 +49784,13 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>3961.63</v>
+        <v>57068.83</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>907581-33-CM26</t>
+          <t>1533460-50-CM26</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -49805,7 +49805,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -49815,27 +49815,27 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
@@ -49849,13 +49849,13 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>57477</v>
+        <v>3961.63</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>1385462-180-CM26</t>
+          <t>907581-33-CM26</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -49880,27 +49880,27 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
@@ -49914,13 +49914,13 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>6039.25</v>
+        <v>57477</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>188-596-CM26</t>
+          <t>1385462-180-CM26</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -49945,12 +49945,12 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -49960,12 +49960,12 @@
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
@@ -49979,13 +49979,13 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>2235.26</v>
+        <v>6039.25</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>765-205-CM26</t>
+          <t>188-596-CM26</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -50000,37 +50000,37 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
@@ -50044,7 +50044,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>183483.72</v>
+        <v>2235.26</v>
       </c>
     </row>
     <row r="766">
@@ -50115,7 +50115,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>894778-42-CM26</t>
+          <t>2348-421-CM26</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -50140,27 +50140,27 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K767" t="inlineStr">
@@ -50174,13 +50174,13 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>332367</v>
+        <v>152784.1</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2348-421-CM26</t>
+          <t>894778-42-CM26</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -50205,41 +50205,171 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
         <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M768" s="2" t="n">
+        <v>332367</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>765-205-CM26</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
           <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
-      <c r="J768" t="inlineStr">
+      <c r="J769" t="inlineStr">
         <is>
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L768" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M768" s="2" t="n">
-        <v>152784.1</v>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M769" s="2" t="n">
+        <v>183483.72</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>894778-43-SE26</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M770" s="2" t="n">
+        <v>30212.91</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-proveedores/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-proveedores/licencia-de-software-de-ofimatica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M793"/>
+  <dimension ref="A1:M794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1392,11 @@
           <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>TECNOLOGIA BS SPA</t>
@@ -16383,7 +16387,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4044-655-CM25</t>
+          <t>3705-413-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16403,22 +16407,22 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>69.061.800-1</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -16442,7 +16446,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>53116.25</v>
+        <v>15393.84</v>
       </c>
     </row>
     <row r="248">
@@ -16513,7 +16517,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3705-413-CM25</t>
+          <t>4044-655-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16533,22 +16537,22 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -16572,7 +16576,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>15393.84</v>
+        <v>53116.25</v>
       </c>
     </row>
     <row r="250">
@@ -17744,7 +17748,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1725-5533-CM25</t>
+          <t>1347870-167-CM25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17764,48 +17768,52 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>346215.74</v>
+        <v>29606.49</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1347870-167-CM25</t>
+          <t>1725-5533-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17825,46 +17833,42 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>29606.49</v>
+        <v>346215.74</v>
       </c>
     </row>
     <row r="270">
@@ -28177,7 +28181,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>4099-13-CM26</t>
+          <t>2436-10-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28197,22 +28201,22 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>69.073.300-5</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -28236,13 +28240,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>13127.98</v>
+        <v>36561.68</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>603663-5-CM26</t>
+          <t>4099-13-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28267,12 +28271,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>69.073.300-5</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -28301,13 +28305,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>71542.62</v>
+        <v>13127.98</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2436-10-CM26</t>
+          <t>603663-5-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28327,22 +28331,22 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -28366,7 +28370,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>36561.68</v>
+        <v>71542.62</v>
       </c>
     </row>
     <row r="432">
@@ -29282,7 +29286,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>730736-23-CM26</t>
+          <t>3866-3-CM26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -29307,17 +29311,17 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -29341,13 +29345,13 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>13846.96</v>
+        <v>9231.309999999999</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>3866-3-CM26</t>
+          <t>730736-23-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -29372,17 +29376,17 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -29406,7 +29410,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>9231.309999999999</v>
+        <v>13846.96</v>
       </c>
     </row>
     <row r="448">
@@ -29802,7 +29806,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>188-92-CM26</t>
+          <t>1704-946-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29822,22 +29826,22 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -29861,13 +29865,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>8982.120000000001</v>
+        <v>859.89</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1704-946-CM26</t>
+          <t>188-92-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29887,22 +29891,22 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -29926,7 +29930,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>859.89</v>
+        <v>8982.120000000001</v>
       </c>
     </row>
     <row r="456">
@@ -30647,7 +30651,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>568658-365-CM26</t>
+          <t>4052-22-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -30672,17 +30676,17 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -30706,7 +30710,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>30771.02</v>
+        <v>10000.58</v>
       </c>
     </row>
     <row r="468">
@@ -30842,7 +30846,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>4052-22-CM26</t>
+          <t>568658-365-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30867,17 +30871,17 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -30901,7 +30905,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>10000.58</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="471">
@@ -32097,7 +32101,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -32597,7 +32601,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>4256-78-CM26</t>
+          <t>5768-44-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32617,32 +32621,32 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -32656,13 +32660,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>2661.08</v>
+        <v>37485</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>5768-44-CM26</t>
+          <t>4732-64-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32687,27 +32691,27 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
@@ -32721,13 +32725,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>37485</v>
+        <v>14192.42</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>4732-64-CM26</t>
+          <t>4252-84-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32747,22 +32751,22 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -32786,13 +32790,13 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>14192.42</v>
+        <v>9491.18</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>4252-84-CM26</t>
+          <t>4256-78-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32851,7 +32855,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>9491.18</v>
+        <v>2661.08</v>
       </c>
     </row>
     <row r="501">
@@ -35335,7 +35339,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -35660,7 +35664,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -38386,7 +38390,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
@@ -40068,7 +40072,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -40519,7 +40523,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
@@ -41039,7 +41043,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
@@ -41104,7 +41108,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
@@ -41279,7 +41283,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2674-576-CM26</t>
+          <t>1417902-21-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -41299,37 +41303,37 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>65.211.127-0</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>ASOCIACION DE MUNICIPALIDADES DE LA ZONA METROPOLITANA DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
@@ -41338,13 +41342,13 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>4226.17</v>
+        <v>2165.01</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>1609-220-CM26</t>
+          <t>798018-61-CM26</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -41364,32 +41368,32 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>65.073.222-7</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K632" t="inlineStr">
@@ -41403,7 +41407,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>64452.54</v>
+        <v>5077.22</v>
       </c>
     </row>
     <row r="633">
@@ -41429,7 +41433,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
@@ -41559,7 +41563,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
@@ -41864,7 +41868,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>798018-61-CM26</t>
+          <t>2674-576-CM26</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -41889,12 +41893,12 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>65.073.222-7</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -41904,17 +41908,17 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
@@ -41923,13 +41927,13 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>5077.22</v>
+        <v>4226.17</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>1417902-21-CM26</t>
+          <t>1609-220-CM26</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -41954,17 +41958,17 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>65.211.127-0</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES DE LA ZONA METROPOLITANA DE LA ARAUCANIA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -41988,13 +41992,13 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2165.01</v>
+        <v>64452.54</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>539119-2289-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -42014,37 +42018,37 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -42053,13 +42057,13 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>845.23</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>539119-2289-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -42079,52 +42083,52 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I643" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J643" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K643" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>887.03</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>4077-104-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -42149,12 +42153,12 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -42164,17 +42168,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -42183,13 +42187,13 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>6761.87</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>4077-104-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -42209,37 +42213,37 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
@@ -42248,13 +42252,13 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>1031.66</v>
+        <v>6761.87</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>699360-38-CM26</t>
+          <t>1561-110-CM26</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -42279,12 +42283,12 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -42294,32 +42298,28 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K646" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr"/>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>4587.2</v>
+        <v>11195.52</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>1561-109-CM26</t>
+          <t>699360-38-CM26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -42334,22 +42334,22 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -42359,28 +42359,32 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K647" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>142889.96</v>
+        <v>4587.2</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>3442-276-CM26</t>
+          <t>1561-109-CM26</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -42400,52 +42404,48 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K648" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr"/>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>26610.78</v>
+        <v>142889.96</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>3796-350-CM26</t>
+          <t>3442-276-CM26</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -42465,22 +42465,22 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -42504,13 +42504,13 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>35078.96</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>858-254-CM26</t>
+          <t>3796-350-CM26</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -42535,27 +42535,27 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
@@ -42569,13 +42569,13 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>4470.52</v>
+        <v>35078.96</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>3517-103-CM26</t>
+          <t>858-254-CM26</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -42600,27 +42600,27 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -42634,13 +42634,13 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>1774.05</v>
+        <v>4470.52</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>3573-50-CM26</t>
+          <t>3517-103-CM26</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -42655,7 +42655,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -42665,17 +42665,17 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -42699,13 +42699,13 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>36123.64</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>3073-290-CM26</t>
+          <t>3573-50-CM26</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -42720,7 +42720,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -42730,27 +42730,27 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
@@ -42764,13 +42764,13 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>5226.19</v>
+        <v>36123.64</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2582-255-SE26</t>
+          <t>3073-290-CM26</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -42790,32 +42790,32 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -42829,13 +42829,13 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>218562.54</v>
+        <v>5226.19</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2360-474-CM26</t>
+          <t>2582-255-SE26</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -42850,7 +42850,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -42860,32 +42860,32 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
@@ -42894,13 +42894,13 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>7607.1</v>
+        <v>218562.54</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>3420-34-CM26</t>
+          <t>2360-474-CM26</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -42925,17 +42925,17 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>61.101.054-0</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>1901.77</v>
+        <v>7607.1</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2318-537-CM26</t>
+          <t>3420-34-CM26</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -42990,32 +42990,32 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>61.101.054-0</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -43024,13 +43024,13 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>40280.79</v>
+        <v>1901.77</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2923-518-CM26</t>
+          <t>2318-537-CM26</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -43045,7 +43045,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -43055,17 +43055,17 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -43089,13 +43089,13 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>10024.98</v>
+        <v>40280.79</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>1533460-23-CM26</t>
+          <t>2923-518-CM26</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -43120,27 +43120,27 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
@@ -43154,13 +43154,13 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>7130.93</v>
+        <v>10024.98</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2412-433-CM26</t>
+          <t>1533460-23-CM26</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -43175,7 +43175,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -43185,12 +43185,12 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -43200,17 +43200,17 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
@@ -43219,13 +43219,13 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>2324.39</v>
+        <v>7130.93</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>1036569-100-CM26</t>
+          <t>2412-433-CM26</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -43245,37 +43245,37 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L661" t="inlineStr">
@@ -43284,13 +43284,13 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>32309.57</v>
+        <v>2324.39</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>1068038-18-CM26</t>
+          <t>1036569-100-CM26</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -43305,37 +43305,37 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
@@ -43349,13 +43349,13 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>1664.43</v>
+        <v>32309.57</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>1457902-17-CM26</t>
+          <t>889473-1191-CM26</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -43380,27 +43380,27 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
@@ -43414,13 +43414,13 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>2641.09</v>
+        <v>8182.44</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>889473-1191-CM26</t>
+          <t>2483-477-CM26</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -43440,32 +43440,32 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
@@ -43479,13 +43479,13 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>8182.44</v>
+        <v>175629.72</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2483-477-CM26</t>
+          <t>1068038-18-CM26</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -43505,17 +43505,17 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -43525,12 +43525,12 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
@@ -43544,13 +43544,13 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>175629.72</v>
+        <v>1664.43</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2343-337-CM26</t>
+          <t>1457902-17-CM26</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -43565,7 +43565,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -43575,32 +43575,32 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -43609,13 +43609,13 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>4226.17</v>
+        <v>2641.09</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>3251-468-CM26</t>
+          <t>2343-337-CM26</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -43635,37 +43635,37 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L667" t="inlineStr">
@@ -43674,13 +43674,13 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>13733.65</v>
+        <v>4226.17</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>1457282-36-CM26</t>
+          <t>3251-468-CM26</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -43695,37 +43695,37 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>65.011.263-6</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>CORPORACION CENTRO CULTURAL GABRIELA MISTRAL</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
@@ -43739,7 +43739,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>18933.61</v>
+        <v>13733.65</v>
       </c>
     </row>
     <row r="669">
@@ -43810,7 +43810,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>3996-373-CM26</t>
+          <t>1457282-36-CM26</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -43835,17 +43835,17 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>65.011.263-6</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>CORPORACION CENTRO CULTURAL GABRIELA MISTRAL</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -43869,13 +43869,13 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>7983.23</v>
+        <v>18933.61</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2724-595-CM26</t>
+          <t>3996-373-CM26</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -43890,27 +43890,27 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -43934,13 +43934,13 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>35481.04</v>
+        <v>7983.23</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2098-1687-CM26</t>
+          <t>2724-595-CM26</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -43965,17 +43965,17 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>61.602.211-3</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -43999,13 +43999,13 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>74302.77</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>4357-214-CM26</t>
+          <t>2098-1687-CM26</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -44020,27 +44020,27 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.602.211-3</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -44064,13 +44064,13 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>3846.38</v>
+        <v>74302.77</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>3420-37-CM26</t>
+          <t>4357-214-CM26</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -44090,37 +44090,37 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>61.101.054-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
@@ -44129,13 +44129,13 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>21976.06</v>
+        <v>3846.38</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>3479-1147-CM26</t>
+          <t>3420-37-CM26</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -44150,42 +44150,42 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>61.101.054-0</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L675" t="inlineStr">
@@ -44194,13 +44194,13 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>7923.26</v>
+        <v>21976.06</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>585-94-CM26</t>
+          <t>3479-1147-CM26</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -44215,7 +44215,7 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -44225,27 +44225,27 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
@@ -44259,13 +44259,13 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>326243.38</v>
+        <v>7923.26</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>4189-468-CM26</t>
+          <t>585-94-CM26</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -44280,7 +44280,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -44290,27 +44290,27 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
@@ -44324,13 +44324,13 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>15079.44</v>
+        <v>326243.38</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>3731-192-CM26</t>
+          <t>1195-439-CM26</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -44350,32 +44350,32 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
@@ -44389,13 +44389,13 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>6886.53</v>
+        <v>6062.46</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>1195-439-CM26</t>
+          <t>3731-192-CM26</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -44420,27 +44420,27 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
@@ -44454,13 +44454,13 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>6062.46</v>
+        <v>6886.53</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>3300-99-CM26</t>
+          <t>4189-468-CM26</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -44470,32 +44470,32 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -44519,13 +44519,13 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>7096.21</v>
+        <v>15079.44</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>858-299-CM26</t>
+          <t>3300-99-CM26</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -44550,27 +44550,27 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
@@ -44584,13 +44584,13 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>24072.03</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>5147-233-CM26</t>
+          <t>858-299-CM26</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -44610,32 +44610,32 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
@@ -44649,13 +44649,13 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>7083.59</v>
+        <v>24072.03</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>3690-213-CM26</t>
+          <t>5147-233-CM26</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -44670,7 +44670,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -44680,17 +44680,17 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -44714,13 +44714,13 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>14779.8</v>
+        <v>7083.59</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2732-21-CM26</t>
+          <t>3690-213-CM26</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -44745,27 +44745,27 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
@@ -44779,13 +44779,13 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>165430.94</v>
+        <v>14779.8</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>1750-263-CM26</t>
+          <t>2732-21-CM26</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -44805,17 +44805,17 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -44844,13 +44844,13 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>10644.31</v>
+        <v>165430.94</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>1606-281-CM26</t>
+          <t>1750-263-CM26</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -44875,12 +44875,12 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -44890,12 +44890,12 @@
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
@@ -44909,13 +44909,13 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>6082.09</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>3084-121-CM26</t>
+          <t>1606-281-CM26</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -44940,27 +44940,27 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
@@ -44974,13 +44974,13 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>77339.91</v>
+        <v>6082.09</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>539119-2520-CM26</t>
+          <t>3084-121-CM26</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -45005,32 +45005,32 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L688" t="inlineStr">
@@ -45039,13 +45039,13 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>845.23</v>
+        <v>77339.91</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>3946-315-CM26</t>
+          <t>539119-2520-CM26</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -45065,37 +45065,37 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
@@ -45104,13 +45104,13 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>1377.31</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>1529-215-CM26</t>
+          <t>3946-315-CM26</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -45130,17 +45130,17 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -45150,12 +45150,12 @@
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
@@ -45169,13 +45169,13 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>30771.02</v>
+        <v>1377.31</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>3134-170-CM26</t>
+          <t>1529-215-CM26</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -45200,17 +45200,17 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -45234,13 +45234,13 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>15079.44</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>797305-49-CM26</t>
+          <t>3134-170-CM26</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -45265,27 +45265,27 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
@@ -45299,13 +45299,13 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>76020.17999999999</v>
+        <v>15079.44</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>3894-65-CM26</t>
+          <t>797305-49-CM26</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -45320,22 +45320,22 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -45345,12 +45345,12 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -45364,13 +45364,13 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>64867.5</v>
+        <v>76020.17999999999</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>595636-60-CM26</t>
+          <t>3894-65-CM26</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -45395,12 +45395,12 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -45410,17 +45410,17 @@
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K694" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L694" t="inlineStr">
@@ -45429,13 +45429,13 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>845.23</v>
+        <v>64867.5</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>604944-82-CM26</t>
+          <t>595636-60-CM26</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -45455,17 +45455,17 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -45475,17 +45475,17 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
@@ -45494,13 +45494,13 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>11132.26</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2292-6894-CM26</t>
+          <t>604944-82-CM26</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -45515,42 +45515,42 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
@@ -45559,13 +45559,13 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>2747.01</v>
+        <v>11132.26</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>3705-389-CM26</t>
+          <t>2292-6894-CM26</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -45590,32 +45590,32 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -45624,13 +45624,13 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>16924.06</v>
+        <v>2747.01</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>3606-145-CM26</t>
+          <t>3705-389-CM26</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -45645,27 +45645,27 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>61.967.400-6</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -45689,13 +45689,13 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>4878.64</v>
+        <v>16924.06</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>1271178-266-CM26</t>
+          <t>3606-145-CM26</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -45710,42 +45710,42 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>61.967.400-6</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L699" t="inlineStr">
@@ -45754,13 +45754,13 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>1479.16</v>
+        <v>4878.64</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>3997-306-CM26</t>
+          <t>1271178-266-CM26</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -45780,37 +45780,37 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
@@ -45819,13 +45819,13 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>14635.93</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>1237849-145-CM26</t>
+          <t>3997-306-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -45845,22 +45845,22 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>65.081.056-2</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -45884,13 +45884,13 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>3077.1</v>
+        <v>14635.93</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>4177-92-CM26</t>
+          <t>1237849-145-CM26</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -45910,32 +45910,32 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>65.081.056-2</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K702" t="inlineStr">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>8769.74</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>1750-284-CM26</t>
+          <t>4177-92-CM26</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -45970,37 +45970,37 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
@@ -46014,13 +46014,13 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>46156.53</v>
+        <v>8769.74</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>937232-578-CM26</t>
+          <t>1750-284-CM26</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -46035,22 +46035,22 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -46060,12 +46060,12 @@
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K704" t="inlineStr">
@@ -46079,13 +46079,13 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2112.87</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>1078177-724-CM26</t>
+          <t>937232-578-CM26</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -46105,37 +46105,37 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L705" t="inlineStr">
@@ -46144,13 +46144,13 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2113.08</v>
+        <v>2112.87</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>1121-83-CM26</t>
+          <t>1078177-724-CM26</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -46165,7 +46165,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -46175,32 +46175,32 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L706" t="inlineStr">
@@ -46209,13 +46209,13 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>30913.52</v>
+        <v>2113.08</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>1121-84-CM26</t>
+          <t>1121-83-CM26</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -46255,12 +46255,12 @@
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
@@ -46274,13 +46274,13 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>7909.38</v>
+        <v>30913.52</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>1393575-77-CM26</t>
+          <t>1121-84-CM26</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -46305,12 +46305,12 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -46320,12 +46320,12 @@
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
@@ -46339,13 +46339,13 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>1422.05</v>
+        <v>7909.38</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>1287766-76-CM26</t>
+          <t>1393575-77-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -46365,17 +46365,17 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>65.199.980-4</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Ñuñoa</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -46385,12 +46385,12 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
@@ -46404,13 +46404,13 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>4080.32</v>
+        <v>1422.05</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>4494-608-CM26</t>
+          <t>1287766-76-CM26</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -46435,17 +46435,17 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>65.199.980-4</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>Corporación Municipal de Deportes de Ñuñoa</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -46469,13 +46469,13 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>35481.04</v>
+        <v>4080.32</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>872535-246-CM26</t>
+          <t>4494-608-CM26</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -46495,22 +46495,22 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -46534,13 +46534,13 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>49233.63</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>1723-493-CM26</t>
+          <t>872535-246-CM26</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -46555,42 +46555,42 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
@@ -46599,13 +46599,13 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>1056.54</v>
+        <v>49233.63</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>836-127-CM26</t>
+          <t>1723-493-CM26</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -46630,47 +46630,47 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I713" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J713" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K713" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>46156.53</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>857-121-CM26</t>
+          <t>836-127-CM26</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -46685,7 +46685,7 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
@@ -46695,17 +46695,17 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>72.576.700-5</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -46729,13 +46729,13 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>50772.18</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>751-300-CM26</t>
+          <t>857-121-CM26</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -46755,32 +46755,32 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>72.576.700-5</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
@@ -46794,13 +46794,13 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>21124.88</v>
+        <v>50772.18</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>4246-85-CM26</t>
+          <t>751-300-CM26</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -46815,7 +46815,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -46825,27 +46825,27 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>61.976.100-6</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
@@ -46859,13 +46859,13 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>21128.69</v>
+        <v>21124.88</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>1375746-102-CM26</t>
+          <t>4246-85-CM26</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -46890,12 +46890,12 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>61.976.100-6</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -46905,12 +46905,12 @@
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
@@ -46924,13 +46924,13 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>16260.16</v>
+        <v>21128.69</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>688-100-CM26</t>
+          <t>1375746-102-CM26</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -46950,17 +46950,17 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -46970,12 +46970,12 @@
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
@@ -46989,13 +46989,13 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>71574.92999999999</v>
+        <v>16260.16</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>514862-530-CM26</t>
+          <t>688-100-CM26</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -47010,22 +47010,22 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -47035,17 +47035,17 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
@@ -47054,13 +47054,13 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>1901.77</v>
+        <v>71574.92999999999</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>4323-198-CM26</t>
+          <t>514862-530-CM26</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -47075,27 +47075,27 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -47119,13 +47119,13 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>1056.54</v>
+        <v>1901.77</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>1079713-481-CM26</t>
+          <t>4323-198-CM26</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -47150,17 +47150,17 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>53.322.604-3</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -47190,7 +47190,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>1375757-515-CM26</t>
+          <t>1079713-481-CM26</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -47210,17 +47210,17 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>53.322.604-3</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -47230,17 +47230,17 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
@@ -47249,13 +47249,13 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>12580.68</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>1202333-127-CM26</t>
+          <t>1375757-515-CM26</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -47280,32 +47280,32 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>69.060.700-K</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
@@ -47314,13 +47314,13 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>27892.7</v>
+        <v>12580.68</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>4170-239-CM26</t>
+          <t>1202333-127-CM26</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -47345,32 +47345,32 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.060.700-K</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
@@ -47379,13 +47379,13 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>30771.02</v>
+        <v>27892.7</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>1375761-1560-CM26</t>
+          <t>4170-239-CM26</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -47400,37 +47400,37 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
@@ -47444,13 +47444,13 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>12757.4</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>5019-215-CM26</t>
+          <t>1375761-1560-CM26</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -47475,32 +47475,32 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
@@ -47509,13 +47509,13 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>1267.85</v>
+        <v>12757.4</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>1147293-240-CM26</t>
+          <t>5019-215-CM26</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -47535,37 +47535,37 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
@@ -47574,13 +47574,13 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>17915.39</v>
+        <v>1267.85</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>1260-126-SE26</t>
+          <t>1147293-240-CM26</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -47600,17 +47600,17 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -47620,17 +47620,17 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>Extranjero</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L728" t="inlineStr">
@@ -47639,13 +47639,13 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>106407.42</v>
+        <v>17915.39</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>5066-202-CM26</t>
+          <t>1260-126-SE26</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -47665,37 +47665,37 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Extranjero</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
@@ -47704,13 +47704,13 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>17475.15</v>
+        <v>106407.42</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>188-517-CM26</t>
+          <t>5066-202-CM26</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -47735,27 +47735,27 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
@@ -47769,13 +47769,13 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>5810.39</v>
+        <v>17475.15</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>1175-708-CM26</t>
+          <t>188-517-CM26</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -47790,37 +47790,37 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
@@ -47834,13 +47834,13 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>132839.7</v>
+        <v>5810.39</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2412-522-CM26</t>
+          <t>1175-708-CM26</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -47860,22 +47860,22 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -47899,13 +47899,13 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>74764.49000000001</v>
+        <v>132839.7</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>3428-231-CM26</t>
+          <t>2412-522-CM26</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -47920,7 +47920,7 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -47930,32 +47930,32 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
@@ -47964,13 +47964,13 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>1690.47</v>
+        <v>74764.49000000001</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>4414-1161-CM26</t>
+          <t>3428-231-CM26</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -47990,37 +47990,37 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
@@ -48029,13 +48029,13 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>29687.88</v>
+        <v>1690.47</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>867990-485-CM26</t>
+          <t>4414-1161-CM26</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -48060,27 +48060,27 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
@@ -48094,13 +48094,13 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>224910</v>
+        <v>29687.88</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>858-348-SE26</t>
+          <t>867990-485-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -48125,12 +48125,12 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -48140,12 +48140,12 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
@@ -48159,13 +48159,13 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>713286</v>
+        <v>224910</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2412-528-CM26</t>
+          <t>858-348-SE26</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -48175,12 +48175,12 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
@@ -48190,12 +48190,12 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -48205,17 +48205,17 @@
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
@@ -48224,13 +48224,13 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>10565.42</v>
+        <v>713286</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2799-897-CM26</t>
+          <t>2412-528-CM26</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -48245,7 +48245,7 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -48255,47 +48255,47 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I738" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J738" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K738" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>218446.87</v>
+        <v>10565.42</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>604944-108-CM26</t>
+          <t>2799-897-CM26</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -48315,32 +48315,32 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
@@ -48354,13 +48354,13 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>8388.07</v>
+        <v>218446.87</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2733-421-CM26</t>
+          <t>604944-108-CM26</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -48375,7 +48375,7 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -48385,12 +48385,12 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -48400,17 +48400,17 @@
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L740" t="inlineStr">
@@ -48419,13 +48419,13 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>6339.25</v>
+        <v>8388.07</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2389-523-CM26</t>
+          <t>2733-421-CM26</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -48450,32 +48450,32 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
@@ -48484,13 +48484,13 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>5111.76</v>
+        <v>6339.25</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2429-1124-CM26</t>
+          <t>2389-523-CM26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -48505,37 +48505,37 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
@@ -48549,13 +48549,13 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>35154.5</v>
+        <v>5111.76</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>3696-241-CM26</t>
+          <t>2429-1124-CM26</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -48570,7 +48570,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -48580,27 +48580,27 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
@@ -48614,13 +48614,13 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>8923.6</v>
+        <v>35154.5</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>3880-448-CM26</t>
+          <t>3696-241-CM26</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -48640,17 +48640,17 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -48679,13 +48679,13 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>26610.78</v>
+        <v>8923.6</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>595636-75-CM26</t>
+          <t>3880-448-CM26</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -48710,17 +48710,17 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -48744,13 +48744,13 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>62978.85</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>3756-648-CM26</t>
+          <t>595636-75-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -48775,27 +48775,27 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
@@ -48809,13 +48809,13 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>10335.15</v>
+        <v>62978.85</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>1049-1453-CM26</t>
+          <t>3756-648-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -48840,27 +48840,27 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>61.310.000-8</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>INSTITUTO DE FOMENTO PESQUERO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
@@ -48874,13 +48874,13 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>2579.15</v>
+        <v>10335.15</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2409-1109-CM26</t>
+          <t>1049-1453-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -48905,27 +48905,27 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>61.310.000-8</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>INSTITUTO DE FOMENTO PESQUERO</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
@@ -48939,13 +48939,13 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>22175.65</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>734-655-CM26</t>
+          <t>2409-1109-CM26</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -48970,27 +48970,27 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
@@ -49004,13 +49004,13 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>293254.08</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>1080157-134-CM26</t>
+          <t>734-655-CM26</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -49030,37 +49030,37 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K750" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L750" t="inlineStr">
@@ -49069,13 +49069,13 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>2747.01</v>
+        <v>293254.08</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2305-63-CM26</t>
+          <t>1080157-134-CM26</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -49090,7 +49090,7 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -49100,32 +49100,32 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L751" t="inlineStr">
@@ -49134,13 +49134,13 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>5158.29</v>
+        <v>2747.01</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>4728-326-CM26</t>
+          <t>2305-63-CM26</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -49165,17 +49165,17 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>60.719.000-3</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -49199,13 +49199,13 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>7221.61</v>
+        <v>5158.29</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>3695-420-CM26</t>
+          <t>4728-326-CM26</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -49230,27 +49230,27 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>60.719.000-3</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K753" t="inlineStr">
@@ -49264,13 +49264,13 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>923.13</v>
+        <v>7221.61</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2434-37-CM26</t>
+          <t>3695-420-CM26</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -49285,37 +49285,37 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
@@ -49329,13 +49329,13 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>120303.05</v>
+        <v>923.13</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>979-1248-CM26</t>
+          <t>2434-37-CM26</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -49360,12 +49360,12 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -49375,12 +49375,12 @@
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K755" t="inlineStr">
@@ -49394,13 +49394,13 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>28709.51</v>
+        <v>120303.05</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2981-1144-CM26</t>
+          <t>979-1248-CM26</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -49420,17 +49420,17 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -49459,13 +49459,13 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>5772.69</v>
+        <v>28709.51</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>619284-146-CM26</t>
+          <t>2981-1144-CM26</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -49480,22 +49480,22 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>61.980.000-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -49505,12 +49505,12 @@
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
@@ -49524,13 +49524,13 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>2751.09</v>
+        <v>5772.69</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>1057448-421-CM26</t>
+          <t>619284-146-CM26</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -49555,17 +49555,17 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.980.000-1</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -49589,13 +49589,13 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>8979.690000000001</v>
+        <v>2751.09</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2906-131-CM26</t>
+          <t>1057448-421-CM26</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -49620,27 +49620,27 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
@@ -49654,13 +49654,13 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>26610.78</v>
+        <v>8979.690000000001</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>3674-585-CM26</t>
+          <t>2906-131-CM26</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -49685,27 +49685,27 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
@@ -49719,13 +49719,13 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>17577.25</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>872-572-CM26</t>
+          <t>3674-585-CM26</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -49740,37 +49740,37 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>ORION 2000 SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>96.899.890-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
@@ -49784,13 +49784,13 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>57068.83</v>
+        <v>17577.25</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>1533460-50-CM26</t>
+          <t>872-572-CM26</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -49805,22 +49805,22 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -49830,12 +49830,12 @@
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.899.890-0</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
@@ -49849,13 +49849,13 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>3961.63</v>
+        <v>57068.83</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>188-596-CM26</t>
+          <t>1533460-50-CM26</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -49870,7 +49870,7 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -49880,12 +49880,12 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -49914,13 +49914,13 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>2235.26</v>
+        <v>3961.63</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>907581-33-CM26</t>
+          <t>188-596-CM26</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -49945,27 +49945,27 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
@@ -49979,13 +49979,13 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>57477</v>
+        <v>2235.26</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>1385462-180-CM26</t>
+          <t>907581-33-CM26</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -50005,32 +50005,32 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
@@ -50044,13 +50044,13 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>6039.25</v>
+        <v>57477</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>894778-42-CM26</t>
+          <t>1385462-180-CM26</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -50065,7 +50065,7 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -50075,12 +50075,12 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -50090,12 +50090,12 @@
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
@@ -50109,13 +50109,13 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>332367</v>
+        <v>6039.25</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>765-205-CM26</t>
+          <t>894778-42-CM26</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -50140,27 +50140,27 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K767" t="inlineStr">
@@ -50174,13 +50174,13 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>183483.72</v>
+        <v>332367</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>4044-689-CM26</t>
+          <t>765-205-CM26</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -50205,27 +50205,27 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>69.061.800-1</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
@@ -50239,13 +50239,13 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>58970.45</v>
+        <v>183483.72</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2348-421-CM26</t>
+          <t>4044-689-CM26</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -50270,27 +50270,27 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K769" t="inlineStr">
@@ -50304,13 +50304,13 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>152784.1</v>
+        <v>58970.45</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>812261-1397-CM26</t>
+          <t>2348-421-CM26</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -50325,53 +50325,57 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K770" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>223910.4</v>
+        <v>152784.1</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>894778-43-SE26</t>
+          <t>812261-1397-CM26</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -50391,17 +50395,17 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -50411,32 +50415,28 @@
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K771" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr"/>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>30212.91</v>
+        <v>223910.4</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>743848-35-CM26</t>
+          <t>894778-43-SE26</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -50446,27 +50446,27 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>61.980.250-0</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>SEGUNDO TRIBUNAL AMBIENTAL</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -50476,12 +50476,12 @@
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K772" t="inlineStr">
@@ -50495,13 +50495,13 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>19038.1</v>
+        <v>30212.91</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>857-148-CM26</t>
+          <t>743848-35-CM26</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -50526,12 +50526,12 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>72.576.700-5</t>
+          <t>61.980.250-0</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
+          <t>SEGUNDO TRIBUNAL AMBIENTAL</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -50541,12 +50541,12 @@
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K773" t="inlineStr">
@@ -50560,13 +50560,13 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>19335.95</v>
+        <v>19038.1</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2404-1169-CM26</t>
+          <t>857-148-CM26</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -50581,7 +50581,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -50591,17 +50591,17 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>72.576.700-5</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -50625,13 +50625,13 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>20673.87</v>
+        <v>19335.95</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2736-381-CM26</t>
+          <t>2404-1169-CM26</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -50656,27 +50656,27 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K775" t="inlineStr">
@@ -50690,13 +50690,13 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>72311.89999999999</v>
+        <v>20673.87</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2287-784-CM26</t>
+          <t>2736-381-CM26</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -50711,7 +50711,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -50721,27 +50721,27 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K776" t="inlineStr">
@@ -50755,13 +50755,13 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>23436.34</v>
+        <v>72311.89999999999</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>1301883-261-CM26</t>
+          <t>2287-784-CM26</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -50776,7 +50776,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -50786,12 +50786,12 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="I777" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K777" t="inlineStr">
@@ -50820,13 +50820,13 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>2751.09</v>
+        <v>23436.34</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>1029940-84-CM26</t>
+          <t>1301883-261-CM26</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -50851,12 +50851,12 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>62.000.370-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -50866,12 +50866,12 @@
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
@@ -50885,13 +50885,13 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>12772.39</v>
+        <v>2751.09</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>1561-180-CM26</t>
+          <t>1029940-84-CM26</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -50916,12 +50916,12 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>62.000.370-0</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
@@ -50931,12 +50931,12 @@
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K779" t="inlineStr">
@@ -50950,13 +50950,13 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>8597.16</v>
+        <v>12772.39</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>1305532-101-CM26</t>
+          <t>1561-180-CM26</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -50971,7 +50971,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -50981,27 +50981,27 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K780" t="inlineStr">
@@ -51015,13 +51015,13 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>18445</v>
+        <v>8597.16</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>539119-3323-CM26</t>
+          <t>1305532-101-CM26</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -51046,17 +51046,17 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -51080,13 +51080,13 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>1171.82</v>
+        <v>18445</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>3776-516-CM26</t>
+          <t>539119-3323-CM26</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -51111,17 +51111,17 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -51151,7 +51151,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>4121-82-CM26</t>
+          <t>3776-516-CM26</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -51166,7 +51166,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -51176,27 +51176,27 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
@@ -51210,13 +51210,13 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>1079.57</v>
+        <v>1171.82</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>1233616-1906-CM26</t>
+          <t>4121-82-CM26</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -51241,12 +51241,12 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -51256,12 +51256,12 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
@@ -51275,13 +51275,13 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>46131.54</v>
+        <v>1079.57</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>628-114-CM26</t>
+          <t>1233616-1906-CM26</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -51296,7 +51296,7 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -51306,27 +51306,27 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
@@ -51340,13 +51340,13 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>94562.16</v>
+        <v>46131.54</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>1020-334-CM26</t>
+          <t>628-114-CM26</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -51361,7 +51361,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -51371,12 +51371,12 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -51405,13 +51405,13 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>1692.41</v>
+        <v>94562.16</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2153-631-CM26</t>
+          <t>1020-334-CM26</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -51436,12 +51436,12 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>61.608.503-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>Hospital Sanatorio San José de Maipo</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -51451,12 +51451,12 @@
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K787" t="inlineStr">
@@ -51470,13 +51470,13 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>15655.64</v>
+        <v>1692.41</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>4295-88-CM26</t>
+          <t>2153-631-CM26</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -51491,7 +51491,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -51501,27 +51501,27 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.608.503-4</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>Hospital Sanatorio San José de Maipo</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K788" t="inlineStr">
@@ -51535,13 +51535,13 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>388312.61</v>
+        <v>15655.64</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2132-339-CM26</t>
+          <t>4295-88-CM26</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -51556,7 +51556,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -51566,27 +51566,27 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K789" t="inlineStr">
@@ -51600,13 +51600,13 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>1431.53</v>
+        <v>388312.61</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>1230771-41-CM26</t>
+          <t>2132-339-CM26</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -51621,7 +51621,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -51631,27 +51631,27 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>65.080.277-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K790" t="inlineStr">
@@ -51665,13 +51665,13 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>1774.05</v>
+        <v>1431.53</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>701-631-CM26</t>
+          <t>1230771-41-CM26</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -51696,27 +51696,27 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>65.080.277-2</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K791" t="inlineStr">
@@ -51730,13 +51730,13 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>20230.48</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>4931-123-CM26</t>
+          <t>701-631-CM26</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -51751,7 +51751,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -51761,17 +51761,17 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>65.613.130-6</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -51795,71 +51795,136 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>1719.43</v>
+        <v>20230.48</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
+          <t>4931-123-CM26</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>65.613.130-6</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M793" s="2" t="n">
+        <v>1719.43</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
           <t>2982-90-CM26</t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C793" t="inlineStr">
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr">
+      <c r="D794" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E793" t="inlineStr">
+      <c r="E794" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F793" t="inlineStr">
+      <c r="F794" t="inlineStr">
         <is>
           <t>60.506.000-5</t>
         </is>
       </c>
-      <c r="G793" t="inlineStr">
+      <c r="G794" t="inlineStr">
         <is>
           <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
-      <c r="H793" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I793" t="inlineStr">
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
         <is>
           <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
-      <c r="J793" t="inlineStr">
+      <c r="J794" t="inlineStr">
         <is>
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L793" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M793" s="2" t="n">
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M794" s="2" t="n">
         <v>7481.38</v>
       </c>
     </row>

--- a/docs/oc-top-proveedores/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-proveedores/licencia-de-software-de-ofimatica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M794"/>
+  <dimension ref="A1:M796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16452,7 +16452,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>688-173-CM25</t>
+          <t>4044-655-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16477,27 +16477,27 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -16511,13 +16511,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>71582.07000000001</v>
+        <v>53116.25</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>4044-655-CM25</t>
+          <t>688-173-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16542,27 +16542,27 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>69.061.800-1</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -16576,7 +16576,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>53116.25</v>
+        <v>71582.07000000001</v>
       </c>
     </row>
     <row r="250">
@@ -27856,7 +27856,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>697-8-CM26</t>
+          <t>3638-1-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27876,17 +27876,17 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -27915,7 +27915,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>16616.35</v>
+        <v>19231.89</v>
       </c>
     </row>
     <row r="425">
@@ -27986,7 +27986,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>3638-1-CM26</t>
+          <t>697-8-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -28006,17 +28006,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -28045,13 +28045,13 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>19231.89</v>
+        <v>16616.35</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>4858-12-CM26</t>
+          <t>4099-13-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -28071,32 +28071,32 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.073.300-5</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
@@ -28110,13 +28110,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>19982.48</v>
+        <v>13127.98</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>3946-7-CM26</t>
+          <t>2436-10-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -28141,27 +28141,27 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -28175,13 +28175,13 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>18546.51</v>
+        <v>36561.68</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2436-10-CM26</t>
+          <t>603663-5-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28201,22 +28201,22 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -28240,13 +28240,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>36561.68</v>
+        <v>71542.62</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>4099-13-CM26</t>
+          <t>4858-12-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28266,32 +28266,32 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>69.073.300-5</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -28305,13 +28305,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>13127.98</v>
+        <v>19982.48</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>603663-5-CM26</t>
+          <t>3946-7-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28331,32 +28331,32 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -28370,7 +28370,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>71542.62</v>
+        <v>18546.51</v>
       </c>
     </row>
     <row r="432">
@@ -28571,7 +28571,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>758-27-CM26</t>
+          <t>3791-8-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -28596,27 +28596,27 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -28630,13 +28630,13 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>15618.99</v>
+        <v>28690.9</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>3791-8-CM26</t>
+          <t>758-27-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -28661,27 +28661,27 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -28695,7 +28695,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>28690.9</v>
+        <v>15618.99</v>
       </c>
     </row>
     <row r="437">
@@ -29286,7 +29286,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>3866-3-CM26</t>
+          <t>730736-23-CM26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -29311,17 +29311,17 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -29345,13 +29345,13 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>9231.309999999999</v>
+        <v>13846.96</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>730736-23-CM26</t>
+          <t>3866-3-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -29376,17 +29376,17 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -29410,7 +29410,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>13846.96</v>
+        <v>9231.309999999999</v>
       </c>
     </row>
     <row r="448">
@@ -29806,7 +29806,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1704-946-CM26</t>
+          <t>2675-29-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29831,27 +29831,27 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
@@ -29865,7 +29865,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>859.89</v>
+        <v>53849.29</v>
       </c>
     </row>
     <row r="455">
@@ -29936,7 +29936,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2675-29-CM26</t>
+          <t>1704-946-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -29961,27 +29961,27 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
@@ -29995,13 +29995,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>53849.29</v>
+        <v>859.89</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2934-12-CM26</t>
+          <t>1020-29-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -30021,17 +30021,17 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -30060,13 +30060,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>4435.13</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>4401-124-CM26</t>
+          <t>2934-12-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -30086,32 +30086,32 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
@@ -30125,13 +30125,13 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>2875.98</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>1020-29-CM26</t>
+          <t>4401-124-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -30156,27 +30156,27 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
@@ -30190,7 +30190,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>46156.53</v>
+        <v>2875.98</v>
       </c>
     </row>
     <row r="460">
@@ -30521,7 +30521,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2912-80-CM26</t>
+          <t>539119-470-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30541,32 +30541,32 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
@@ -30580,13 +30580,13 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>4435.13</v>
+        <v>1056.9</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>3872-43-CM26</t>
+          <t>1238177-14-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30606,32 +30606,32 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
@@ -30645,13 +30645,13 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1523.2</v>
+        <v>3534.3</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>4052-22-CM26</t>
+          <t>568658-365-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -30676,17 +30676,17 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -30710,13 +30710,13 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>10000.58</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>539119-470-CM26</t>
+          <t>4052-22-CM26</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -30741,27 +30741,27 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -30775,13 +30775,13 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>1056.9</v>
+        <v>10000.58</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>1238177-14-CM26</t>
+          <t>3872-43-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -30801,32 +30801,32 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
@@ -30840,13 +30840,13 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>3534.3</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>568658-365-CM26</t>
+          <t>2912-80-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30866,22 +30866,22 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -30905,13 +30905,13 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>30771.02</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>633-83-CM26</t>
+          <t>2677-49-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -30936,27 +30936,27 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
@@ -30970,13 +30970,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>565653.41</v>
+        <v>37694.5</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2677-49-CM26</t>
+          <t>633-83-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -31001,27 +31001,27 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
@@ -31035,7 +31035,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>37694.5</v>
+        <v>565653.41</v>
       </c>
     </row>
     <row r="473">
@@ -32016,7 +32016,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>4085-152-CM26</t>
+          <t>1398-197-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -32036,32 +32036,32 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>12404.04</v>
+        <v>102645.59</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>1398-197-CM26</t>
+          <t>4085-152-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32101,32 +32101,32 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
@@ -32140,7 +32140,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>102645.59</v>
+        <v>12404.04</v>
       </c>
     </row>
     <row r="490">
@@ -32601,7 +32601,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>5768-44-CM26</t>
+          <t>4256-78-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32621,32 +32621,32 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -32660,13 +32660,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>37485</v>
+        <v>2661.08</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>4732-64-CM26</t>
+          <t>5768-44-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32691,27 +32691,27 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
@@ -32725,13 +32725,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>14192.42</v>
+        <v>37485</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>4252-84-CM26</t>
+          <t>4732-64-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32751,22 +32751,22 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>9491.18</v>
+        <v>14192.42</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>4256-78-CM26</t>
+          <t>4252-84-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32855,7 +32855,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>2661.08</v>
+        <v>9491.18</v>
       </c>
     </row>
     <row r="501">
@@ -33182,7 +33182,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>3713-38-CM26</t>
+          <t>728-25-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -33207,32 +33207,32 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.211.000-k</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>INSTITUTO NACIONAL DE HIDRAULICA</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -33241,13 +33241,13 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>2958.82</v>
+        <v>11794.09</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>728-25-CM26</t>
+          <t>1256505-27-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33267,32 +33267,32 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>61.211.000-k</t>
+          <t>71.015.300-0</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE HIDRAULICA</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>11794.09</v>
+        <v>1085.28</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>1256505-27-CM26</t>
+          <t>3713-38-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33332,37 +33332,37 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>71.015.300-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -33371,7 +33371,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1085.28</v>
+        <v>2958.82</v>
       </c>
     </row>
     <row r="509">
@@ -33442,7 +33442,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>722-27-CM26</t>
+          <t>4777-274-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33462,22 +33462,22 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -33501,13 +33501,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>30742.22</v>
+        <v>31045.91</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>4777-274-CM26</t>
+          <t>722-27-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33527,22 +33527,22 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -33566,7 +33566,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>31045.91</v>
+        <v>30742.22</v>
       </c>
     </row>
     <row r="512">
@@ -33702,7 +33702,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>4284-148-CM26</t>
+          <t>4192-33-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33722,32 +33722,32 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
@@ -33761,13 +33761,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>48786.43</v>
+        <v>55827.66</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>4192-33-CM26</t>
+          <t>4284-148-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33787,32 +33787,32 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
@@ -33826,13 +33826,13 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>55827.66</v>
+        <v>48786.43</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2410-54-CM26</t>
+          <t>3707-206-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33857,37 +33857,41 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K516" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>72770.88</v>
+        <v>13393.95</v>
       </c>
     </row>
     <row r="517">
@@ -33958,7 +33962,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>3707-206-CM26</t>
+          <t>2410-54-CM26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -33983,47 +33987,43 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K518" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>13393.95</v>
+        <v>72770.88</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2427-295-CM26</t>
+          <t>3621-125-CM26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -34043,17 +34043,17 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -34063,12 +34063,12 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
@@ -34082,13 +34082,13 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>13205.43</v>
+        <v>17387.27</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2427-296-CM26</t>
+          <t>2427-295-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -34128,28 +34128,32 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K520" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>55977.6</v>
+        <v>13205.43</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>3621-125-CM26</t>
+          <t>2427-296-CM26</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -34169,17 +34173,17 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -34189,32 +34193,28 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K521" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>17387.27</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>1048-124-CM26</t>
+          <t>1300026-9-CM26</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -34234,22 +34234,22 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>65.497.180-3</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>CORP CULTURAL DE LA COMUNA DE LA GRANJA</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -34273,13 +34273,13 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>41279.32</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1300026-9-CM26</t>
+          <t>1048-124-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -34299,22 +34299,22 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>65.497.180-3</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LA COMUNA DE LA GRANJA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -34338,7 +34338,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>1774.05</v>
+        <v>41279.32</v>
       </c>
     </row>
     <row r="524">
@@ -34929,7 +34929,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>542429-19-CM26</t>
+          <t>4294-60-CM26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -34954,32 +34954,32 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>65.077.010-2</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -34988,13 +34988,13 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>7890.56</v>
+        <v>14794.08</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>4294-60-CM26</t>
+          <t>542429-19-CM26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -35019,32 +35019,32 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>65.077.010-2</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -35053,7 +35053,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>14794.08</v>
+        <v>7890.56</v>
       </c>
     </row>
     <row r="535">
@@ -35449,7 +35449,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>4134-274-CM26</t>
+          <t>3708-146-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -35474,27 +35474,27 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
@@ -35508,13 +35508,13 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>22175.65</v>
+        <v>32092.52</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>3708-146-CM26</t>
+          <t>4134-274-CM26</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -35539,27 +35539,27 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
@@ -35573,7 +35573,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>32092.52</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="543">
@@ -35644,7 +35644,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1288-250-CM26</t>
+          <t>3517-60-CM26</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -35664,32 +35664,32 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K544" t="inlineStr">
@@ -35703,13 +35703,13 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>1076.99</v>
+        <v>5588.26</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>3517-60-CM26</t>
+          <t>1288-250-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35729,32 +35729,32 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
@@ -35768,7 +35768,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>5588.26</v>
+        <v>1076.99</v>
       </c>
     </row>
     <row r="546">
@@ -35839,7 +35839,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2713-473-CM26</t>
+          <t>948354-703-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35864,27 +35864,27 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
@@ -35898,13 +35898,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>44351.3</v>
+        <v>21134.4</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>948354-703-CM26</t>
+          <t>2713-473-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -35929,27 +35929,27 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
@@ -35963,7 +35963,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>21134.4</v>
+        <v>44351.3</v>
       </c>
     </row>
     <row r="549">
@@ -36099,7 +36099,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>699360-19-CM26</t>
+          <t>2343-162-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -36124,12 +36124,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -36139,17 +36139,17 @@
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
@@ -36158,13 +36158,13 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>4325.59</v>
+        <v>2536.13</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2343-162-CM26</t>
+          <t>3157-25-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -36189,32 +36189,32 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
@@ -36223,13 +36223,13 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>2536.13</v>
+        <v>1951.46</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>3157-25-CM26</t>
+          <t>699360-19-CM26</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -36254,27 +36254,27 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K553" t="inlineStr">
@@ -36288,7 +36288,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>1951.46</v>
+        <v>4325.59</v>
       </c>
     </row>
     <row r="554">
@@ -36359,7 +36359,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>5684-256-CM26</t>
+          <t>4928-38-CM26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -36384,12 +36384,12 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -36399,12 +36399,12 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K555" t="inlineStr">
@@ -36418,13 +36418,13 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>2461.68</v>
+        <v>4617.6</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>4928-38-CM26</t>
+          <t>5684-256-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -36449,12 +36449,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -36464,12 +36464,12 @@
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
@@ -36483,13 +36483,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>4617.6</v>
+        <v>2461.68</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1057439-3171-CM26</t>
+          <t>1351461-18-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -36514,27 +36514,27 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
@@ -36548,13 +36548,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1596.98</v>
+        <v>26155.37</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1351461-18-CM26</t>
+          <t>3497-231-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -36579,27 +36579,27 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
@@ -36613,13 +36613,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>26155.37</v>
+        <v>1056.72</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>3497-231-CM26</t>
+          <t>1020-136-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -36639,32 +36639,32 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
@@ -36678,13 +36678,13 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>1056.72</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>1020-136-CM26</t>
+          <t>1238177-77-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -36704,17 +36704,17 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -36743,13 +36743,13 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2579.15</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>1238177-77-CM26</t>
+          <t>1057439-3171-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -36774,27 +36774,27 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
@@ -36808,13 +36808,13 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1031.66</v>
+        <v>1596.98</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>1018-58-CM26</t>
+          <t>872-222-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36834,17 +36834,17 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -36854,28 +36854,32 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K562" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>55977.6</v>
+        <v>8453.76</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2678-71-CM26</t>
+          <t>2404-577-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36900,27 +36904,27 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
@@ -36934,13 +36938,13 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>4878.64</v>
+        <v>34026.38</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>872-222-CM26</t>
+          <t>3507-326-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -36960,32 +36964,32 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
@@ -36999,13 +37003,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>8453.76</v>
+        <v>17740.52</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>3507-326-CM26</t>
+          <t>1018-58-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -37030,47 +37034,43 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K565" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr"/>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>17740.52</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2404-577-CM26</t>
+          <t>2678-71-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -37095,27 +37095,27 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
@@ -37129,7 +37129,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>34026.38</v>
+        <v>4878.64</v>
       </c>
     </row>
     <row r="567">
@@ -37200,7 +37200,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2069-4322-CM26</t>
+          <t>4238-132-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -37225,27 +37225,27 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
@@ -37259,13 +37259,13 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>1031.66</v>
+        <v>19514.57</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>4238-132-CM26</t>
+          <t>1233616-932-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -37290,27 +37290,27 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
@@ -37324,13 +37324,13 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>19514.57</v>
+        <v>12195.12</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>1233616-932-CM26</t>
+          <t>2069-4322-CM26</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -37355,27 +37355,27 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
@@ -37389,7 +37389,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>12195.12</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="571">
@@ -37460,7 +37460,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2450-536-CM26</t>
+          <t>2483-191-CM26</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -37480,32 +37480,32 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K572" t="inlineStr">
@@ -37519,13 +37519,13 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>33398.14</v>
+        <v>61542.04</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>1393-250-CM26</t>
+          <t>557639-614-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -37550,27 +37550,27 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
@@ -37584,13 +37584,13 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>1479.41</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2483-191-CM26</t>
+          <t>3838-123-CM26</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -37610,17 +37610,17 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -37630,12 +37630,12 @@
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
@@ -37649,13 +37649,13 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>61542.04</v>
+        <v>4226.88</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>557639-614-CM26</t>
+          <t>2450-536-CM26</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -37675,22 +37675,22 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -37714,13 +37714,13 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1479.41</v>
+        <v>33398.14</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>3838-123-CM26</t>
+          <t>1393-250-CM26</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -37740,32 +37740,32 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K576" t="inlineStr">
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>4226.88</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="577">
@@ -37850,7 +37850,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>976-81-CM26</t>
+          <t>4079-211-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -37875,32 +37875,32 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K578" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
@@ -37909,13 +37909,13 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>69725.08</v>
+        <v>7819.73</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>4079-211-CM26</t>
+          <t>976-81-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -37940,32 +37940,32 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
@@ -37974,7 +37974,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>7819.73</v>
+        <v>69725.08</v>
       </c>
     </row>
     <row r="580">
@@ -38175,7 +38175,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2594-437-CM26</t>
+          <t>3885-206-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -38195,37 +38195,37 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K583" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
@@ -38234,13 +38234,13 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>2113.44</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>3885-206-CM26</t>
+          <t>2594-437-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -38260,37 +38260,37 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
@@ -38299,7 +38299,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>2113.44</v>
       </c>
     </row>
     <row r="585">
@@ -38817,7 +38817,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>568658-841-CM26</t>
+          <t>1084156-411-CM26</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -38842,27 +38842,27 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K593" t="inlineStr">
@@ -38876,13 +38876,13 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>3170.16</v>
+        <v>9346.26</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>1084156-411-CM26</t>
+          <t>705290-1047-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -38907,27 +38907,27 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>61.608.205-1</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K594" t="inlineStr">
@@ -38941,13 +38941,13 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>9346.26</v>
+        <v>44351.3</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>705290-1047-CM26</t>
+          <t>2793-487-CM26</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -38967,17 +38967,17 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>61.608.205-1</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -39006,13 +39006,13 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>44351.3</v>
+        <v>402884.5</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2793-487-CM26</t>
+          <t>568658-841-CM26</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -39032,32 +39032,32 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
@@ -39071,7 +39071,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>402884.5</v>
+        <v>3170.16</v>
       </c>
     </row>
     <row r="597">
@@ -39532,7 +39532,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>3863-185-CM26</t>
+          <t>3678-177-CM26</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -39552,37 +39552,37 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K604" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
@@ -39591,13 +39591,13 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>7819.29</v>
+        <v>14608.44</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>3678-177-CM26</t>
+          <t>3863-185-CM26</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -39617,46 +39617,46 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
         <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I605" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J605" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K605" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>14608.44</v>
+        <v>7819.29</v>
       </c>
     </row>
     <row r="606">
@@ -40052,7 +40052,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2216-273-CM26</t>
+          <t>3553-199-CM26</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -40077,12 +40077,12 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>MOP Dirección General de Concesiones</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -40092,12 +40092,12 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K612" t="inlineStr">
@@ -40111,13 +40111,13 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>104758.73</v>
+        <v>5158.29</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>3553-199-CM26</t>
+          <t>2216-273-CM26</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -40142,12 +40142,12 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -40157,12 +40157,12 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K613" t="inlineStr">
@@ -40176,13 +40176,13 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>5158.29</v>
+        <v>104758.73</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>3515-294-CM26</t>
+          <t>3084-86-SE26</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -40202,17 +40202,17 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -40222,12 +40222,12 @@
       </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K614" t="inlineStr">
@@ -40241,13 +40241,13 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>150600.45</v>
+        <v>51562.03</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>3084-86-SE26</t>
+          <t>3515-294-CM26</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -40267,17 +40267,17 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -40287,12 +40287,12 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K615" t="inlineStr">
@@ -40306,7 +40306,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>51562.03</v>
+        <v>150600.45</v>
       </c>
     </row>
     <row r="616">
@@ -40698,7 +40698,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>1057492-2513-CM26</t>
+          <t>3616-82-CM26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -40718,37 +40718,37 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
@@ -40757,13 +40757,13 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>3169.62</v>
+        <v>6238.42</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>3616-82-CM26</t>
+          <t>1057492-2513-CM26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -40783,37 +40783,37 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
@@ -40822,7 +40822,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>6238.42</v>
+        <v>3169.62</v>
       </c>
     </row>
     <row r="624">
@@ -40893,7 +40893,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>5586-2119-CM26</t>
+          <t>1368-34-CM26</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -40918,27 +40918,27 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
@@ -40952,7 +40952,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>62229.5</v>
+        <v>10769.86</v>
       </c>
     </row>
     <row r="626">
@@ -41088,7 +41088,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>3479-1041-CM26</t>
+          <t>2767-39-CM26</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -41108,32 +41108,32 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
@@ -41147,13 +41147,13 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>15946</v>
+        <v>70764.53999999999</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>1368-34-CM26</t>
+          <t>5586-2119-CM26</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -41178,27 +41178,27 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
@@ -41212,13 +41212,13 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>10769.86</v>
+        <v>62229.5</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2767-39-CM26</t>
+          <t>3479-1041-CM26</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -41238,32 +41238,32 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K630" t="inlineStr">
@@ -41277,13 +41277,13 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>70764.53999999999</v>
+        <v>15946</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>1417902-21-CM26</t>
+          <t>2378-223-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -41303,37 +41303,37 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>65.211.127-0</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES DE LA ZONA METROPOLITANA DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
@@ -41342,13 +41342,13 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>2165.01</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>798018-61-CM26</t>
+          <t>975-207-CM26</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -41368,17 +41368,17 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>65.073.222-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -41388,12 +41388,12 @@
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K632" t="inlineStr">
@@ -41407,13 +41407,13 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>5077.22</v>
+        <v>1375.54</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>1609-221-CM26</t>
+          <t>2021-131-CM26</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -41438,17 +41438,17 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -41472,13 +41472,13 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>12405.21</v>
+        <v>21044.51</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>2727-551-CM26</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -41498,32 +41498,32 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
@@ -41537,13 +41537,13 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>1375.54</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2021-131-CM26</t>
+          <t>307-56-CM26</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -41568,12 +41568,12 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -41583,17 +41583,17 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
@@ -41602,13 +41602,13 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>21044.51</v>
+        <v>2113.08</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2727-551-CM26</t>
+          <t>1417902-21-CM26</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -41628,32 +41628,32 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>65.211.127-0</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>ASOCIACION DE MUNICIPALIDADES DE LA ZONA METROPOLITANA DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
@@ -41667,13 +41667,13 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>7096.21</v>
+        <v>2165.01</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>307-56-CM26</t>
+          <t>2445-2218-CM26</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -41698,17 +41698,17 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -41732,13 +41732,13 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>2113.08</v>
+        <v>4860.09</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2378-223-CM26</t>
+          <t>1609-221-CM26</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -41763,32 +41763,32 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
@@ -41797,13 +41797,13 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1479.16</v>
+        <v>12405.21</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2445-2218-CM26</t>
+          <t>1609-220-CM26</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -41823,37 +41823,37 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
@@ -41862,7 +41862,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>4860.09</v>
+        <v>64452.54</v>
       </c>
     </row>
     <row r="640">
@@ -41933,7 +41933,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>1609-220-CM26</t>
+          <t>798018-61-CM26</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -41953,32 +41953,32 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>65.073.222-7</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
@@ -41992,13 +41992,13 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>64452.54</v>
+        <v>5077.22</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>699360-38-CM26</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -42018,32 +42018,32 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
@@ -42057,13 +42057,13 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>1031.66</v>
+        <v>4587.2</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>539119-2289-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -42083,37 +42083,37 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -42122,13 +42122,13 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>845.23</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>1561-110-CM26</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -42148,52 +42148,48 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K644" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr"/>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>887.03</v>
+        <v>11195.52</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>4077-104-CM26</t>
+          <t>539119-2289-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -42218,7 +42214,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -42228,37 +42224,37 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I645" t="inlineStr">
-        <is>
-          <t>COMPUTACION INTEGRAL S A</t>
-        </is>
-      </c>
-      <c r="J645" t="inlineStr">
-        <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K645" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>6761.87</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>1561-110-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -42278,48 +42274,52 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K646" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>11195.52</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>699360-38-CM26</t>
+          <t>4077-104-CM26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -42344,7 +42344,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -42354,22 +42354,22 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
@@ -42378,13 +42378,13 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>4587.2</v>
+        <v>6761.87</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>1561-109-CM26</t>
+          <t>858-254-CM26</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -42409,12 +42409,12 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -42424,28 +42424,32 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K648" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>142889.96</v>
+        <v>4470.52</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>3442-276-CM26</t>
+          <t>1561-109-CM26</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -42465,52 +42469,48 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K649" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr"/>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>26610.78</v>
+        <v>142889.96</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>3796-350-CM26</t>
+          <t>3442-276-CM26</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -42530,22 +42530,22 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -42569,13 +42569,13 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>35078.96</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>858-254-CM26</t>
+          <t>3517-103-CM26</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -42600,27 +42600,27 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -42634,13 +42634,13 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>4470.52</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>3517-103-CM26</t>
+          <t>3796-350-CM26</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -42665,27 +42665,27 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
@@ -42699,7 +42699,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>1774.05</v>
+        <v>35078.96</v>
       </c>
     </row>
     <row r="653">
@@ -42770,7 +42770,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>3073-290-CM26</t>
+          <t>2582-255-SE26</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -42795,27 +42795,27 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -42829,13 +42829,13 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>5226.19</v>
+        <v>218562.54</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2582-255-SE26</t>
+          <t>3073-290-CM26</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -42860,27 +42860,27 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
@@ -42894,13 +42894,13 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>218562.54</v>
+        <v>5226.19</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2360-474-CM26</t>
+          <t>2318-537-CM26</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -42925,32 +42925,32 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>7607.1</v>
+        <v>40280.79</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>3420-34-CM26</t>
+          <t>2360-474-CM26</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -42990,17 +42990,17 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>61.101.054-0</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -43024,13 +43024,13 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>1901.77</v>
+        <v>7607.1</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2318-537-CM26</t>
+          <t>3420-34-CM26</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -43055,32 +43055,32 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>61.101.054-0</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
@@ -43089,7 +43089,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>40280.79</v>
+        <v>1901.77</v>
       </c>
     </row>
     <row r="659">
@@ -43355,7 +43355,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>889473-1191-CM26</t>
+          <t>2483-477-CM26</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -43375,32 +43375,32 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
@@ -43414,13 +43414,13 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>8182.44</v>
+        <v>175629.72</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2483-477-CM26</t>
+          <t>1457902-17-CM26</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -43440,32 +43440,32 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
@@ -43479,13 +43479,13 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>175629.72</v>
+        <v>2641.09</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>1068038-18-CM26</t>
+          <t>889473-1191-CM26</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -43510,27 +43510,27 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
@@ -43544,13 +43544,13 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>1664.43</v>
+        <v>8182.44</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>1457902-17-CM26</t>
+          <t>1068038-18-CM26</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -43575,7 +43575,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -43585,7 +43585,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -43609,7 +43609,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>2641.09</v>
+        <v>1664.43</v>
       </c>
     </row>
     <row r="667">
@@ -43810,7 +43810,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>1457282-36-CM26</t>
+          <t>3996-373-CM26</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -43835,17 +43835,17 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>65.011.263-6</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>CORPORACION CENTRO CULTURAL GABRIELA MISTRAL</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -43869,13 +43869,13 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>18933.61</v>
+        <v>7983.23</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>3996-373-CM26</t>
+          <t>1457282-36-CM26</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -43900,17 +43900,17 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>65.011.263-6</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>CORPORACION CENTRO CULTURAL GABRIELA MISTRAL</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -43934,7 +43934,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>7983.23</v>
+        <v>18933.61</v>
       </c>
     </row>
     <row r="672">
@@ -44330,7 +44330,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>1195-439-CM26</t>
+          <t>4189-468-CM26</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -44350,32 +44350,32 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
@@ -44389,13 +44389,13 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>6062.46</v>
+        <v>15079.44</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>3731-192-CM26</t>
+          <t>1195-439-CM26</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -44420,27 +44420,27 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
@@ -44454,13 +44454,13 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>6886.53</v>
+        <v>6062.46</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>4189-468-CM26</t>
+          <t>3731-192-CM26</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -44480,32 +44480,32 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K680" t="inlineStr">
@@ -44519,7 +44519,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>15079.44</v>
+        <v>6886.53</v>
       </c>
     </row>
     <row r="681">
@@ -44720,7 +44720,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>3690-213-CM26</t>
+          <t>1750-263-CM26</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -44740,32 +44740,32 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
@@ -44779,13 +44779,13 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>14779.8</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2732-21-CM26</t>
+          <t>3690-213-CM26</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -44810,27 +44810,27 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
@@ -44844,13 +44844,13 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>165430.94</v>
+        <v>14779.8</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>1750-263-CM26</t>
+          <t>2732-21-CM26</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -44870,17 +44870,17 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -44909,7 +44909,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>10644.31</v>
+        <v>165430.94</v>
       </c>
     </row>
     <row r="687">
@@ -45045,7 +45045,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>539119-2520-CM26</t>
+          <t>3946-315-CM26</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -45065,37 +45065,37 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
@@ -45104,13 +45104,13 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>845.23</v>
+        <v>1377.31</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>3946-315-CM26</t>
+          <t>3134-170-CM26</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -45130,32 +45130,32 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
@@ -45169,13 +45169,13 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>1377.31</v>
+        <v>15079.44</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>1529-215-CM26</t>
+          <t>539119-2520-CM26</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -45200,32 +45200,32 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
@@ -45234,13 +45234,13 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>30771.02</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>3134-170-CM26</t>
+          <t>1529-215-CM26</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -45265,17 +45265,17 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -45299,7 +45299,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>15079.44</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="693">
@@ -45370,7 +45370,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>3894-65-CM26</t>
+          <t>604944-82-CM26</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -45390,17 +45390,17 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -45410,12 +45410,12 @@
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K694" t="inlineStr">
@@ -45429,13 +45429,13 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>64867.5</v>
+        <v>11132.26</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>595636-60-CM26</t>
+          <t>3894-65-CM26</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -45460,12 +45460,12 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -45475,17 +45475,17 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
@@ -45494,13 +45494,13 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>845.23</v>
+        <v>64867.5</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>604944-82-CM26</t>
+          <t>595636-60-CM26</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -45520,17 +45520,17 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -45540,17 +45540,17 @@
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
@@ -45559,13 +45559,13 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>11132.26</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2292-6894-CM26</t>
+          <t>3705-389-CM26</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -45590,32 +45590,32 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -45624,13 +45624,13 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>2747.01</v>
+        <v>16924.06</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>3705-389-CM26</t>
+          <t>2292-6894-CM26</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -45655,32 +45655,32 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L698" t="inlineStr">
@@ -45689,7 +45689,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>16924.06</v>
+        <v>2747.01</v>
       </c>
     </row>
     <row r="699">
@@ -45760,7 +45760,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>1271178-266-CM26</t>
+          <t>3997-306-CM26</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -45780,37 +45780,37 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
@@ -45819,13 +45819,13 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>1479.16</v>
+        <v>14635.93</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>3997-306-CM26</t>
+          <t>4177-92-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -45850,27 +45850,27 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
@@ -45884,7 +45884,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>14635.93</v>
+        <v>8769.74</v>
       </c>
     </row>
     <row r="702">
@@ -45955,7 +45955,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>4177-92-CM26</t>
+          <t>1271178-266-CM26</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -45975,37 +45975,37 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L703" t="inlineStr">
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>8769.74</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="704">
@@ -46215,7 +46215,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>1121-83-CM26</t>
+          <t>4494-608-CM26</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -46235,32 +46235,32 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
@@ -46274,13 +46274,13 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>30913.52</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>1121-84-CM26</t>
+          <t>1393575-77-CM26</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -46305,12 +46305,12 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -46320,12 +46320,12 @@
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
@@ -46339,13 +46339,13 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>7909.38</v>
+        <v>1422.05</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>1393575-77-CM26</t>
+          <t>1287766-76-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -46365,17 +46365,17 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>65.199.980-4</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>Corporación Municipal de Deportes de Ñuñoa</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -46385,12 +46385,12 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
@@ -46404,13 +46404,13 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>1422.05</v>
+        <v>4080.32</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>1287766-76-CM26</t>
+          <t>1121-83-CM26</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -46430,17 +46430,17 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>65.199.980-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Ñuñoa</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -46450,12 +46450,12 @@
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
@@ -46469,13 +46469,13 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>4080.32</v>
+        <v>30913.52</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>4494-608-CM26</t>
+          <t>872535-246-CM26</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -46495,22 +46495,22 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -46534,13 +46534,13 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>35481.04</v>
+        <v>49233.63</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>872535-246-CM26</t>
+          <t>1121-84-CM26</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -46565,27 +46565,27 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
@@ -46599,13 +46599,13 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>49233.63</v>
+        <v>7909.38</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>1723-493-CM26</t>
+          <t>836-127-CM26</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -46630,32 +46630,32 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
@@ -46664,13 +46664,13 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1056.54</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>836-127-CM26</t>
+          <t>1723-493-CM26</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -46695,41 +46695,41 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
         <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I714" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J714" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K714" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>46156.53</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="715">
@@ -47190,7 +47190,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>1079713-481-CM26</t>
+          <t>1375757-515-CM26</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -47210,17 +47210,17 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>53.322.604-3</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -47230,17 +47230,17 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
@@ -47249,13 +47249,13 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>1056.54</v>
+        <v>12580.68</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>1375757-515-CM26</t>
+          <t>1202333-127-CM26</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -47280,32 +47280,32 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>69.060.700-K</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
@@ -47314,13 +47314,13 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>12580.68</v>
+        <v>27892.7</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>1202333-127-CM26</t>
+          <t>1079713-481-CM26</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -47340,46 +47340,46 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>69.060.700-K</t>
+          <t>53.322.604-3</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I724" t="inlineStr">
-        <is>
-          <t>COMPUTACION INTEGRAL S A</t>
-        </is>
-      </c>
-      <c r="J724" t="inlineStr">
-        <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K724" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>27892.7</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="725">
@@ -47450,7 +47450,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>1375761-1560-CM26</t>
+          <t>5066-202-CM26</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -47470,32 +47470,32 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
@@ -47509,13 +47509,13 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>12757.4</v>
+        <v>17475.15</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>5019-215-CM26</t>
+          <t>188-517-CM26</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -47535,37 +47535,37 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
@@ -47574,13 +47574,13 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>1267.85</v>
+        <v>5810.39</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>1147293-240-CM26</t>
+          <t>1375761-1560-CM26</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -47600,22 +47600,22 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -47639,13 +47639,13 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>17915.39</v>
+        <v>12757.4</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>1260-126-SE26</t>
+          <t>5019-215-CM26</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -47670,32 +47670,32 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>Extranjero</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
@@ -47704,13 +47704,13 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>106407.42</v>
+        <v>1267.85</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>5066-202-CM26</t>
+          <t>1147293-240-CM26</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -47735,27 +47735,27 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
@@ -47769,13 +47769,13 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>17475.15</v>
+        <v>17915.39</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>188-517-CM26</t>
+          <t>1260-126-SE26</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -47795,17 +47795,17 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -47815,17 +47815,17 @@
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Extranjero</t>
         </is>
       </c>
       <c r="L731" t="inlineStr">
@@ -47834,7 +47834,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>5810.39</v>
+        <v>106407.42</v>
       </c>
     </row>
     <row r="732">
@@ -48685,7 +48685,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>3880-448-CM26</t>
+          <t>595636-75-CM26</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -48710,17 +48710,17 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -48744,13 +48744,13 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>26610.78</v>
+        <v>62978.85</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>595636-75-CM26</t>
+          <t>3880-448-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -48775,17 +48775,17 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -48809,13 +48809,13 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>62978.85</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>3756-648-CM26</t>
+          <t>734-655-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -48840,27 +48840,27 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
@@ -48874,13 +48874,13 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>10335.15</v>
+        <v>293254.08</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>1049-1453-CM26</t>
+          <t>1080157-134-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -48900,17 +48900,17 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>61.310.000-8</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>INSTITUTO DE FOMENTO PESQUERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -48920,17 +48920,17 @@
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L748" t="inlineStr">
@@ -48939,13 +48939,13 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>2579.15</v>
+        <v>2747.01</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2409-1109-CM26</t>
+          <t>3756-648-CM26</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -48970,27 +48970,27 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
@@ -49004,13 +49004,13 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>22175.65</v>
+        <v>10335.15</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>734-655-CM26</t>
+          <t>2409-1109-CM26</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -49035,27 +49035,27 @@
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K750" t="inlineStr">
@@ -49069,13 +49069,13 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>293254.08</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>1080157-134-CM26</t>
+          <t>1049-1453-CM26</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -49095,17 +49095,17 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.310.000-8</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO DE FOMENTO PESQUERO</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -49115,17 +49115,17 @@
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L751" t="inlineStr">
@@ -49134,7 +49134,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>2747.01</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="752">
@@ -49660,7 +49660,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2906-131-CM26</t>
+          <t>3674-585-CM26</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -49685,27 +49685,27 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
@@ -49719,13 +49719,13 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>26610.78</v>
+        <v>17577.25</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>3674-585-CM26</t>
+          <t>2906-131-CM26</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -49750,27 +49750,27 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
@@ -49784,7 +49784,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>17577.25</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="762">
@@ -49875,7 +49875,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
@@ -51021,7 +51021,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>1305532-101-CM26</t>
+          <t>3776-516-CM26</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -51046,17 +51046,17 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -51080,13 +51080,13 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>18445</v>
+        <v>1171.82</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>539119-3323-CM26</t>
+          <t>1305532-101-CM26</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -51111,17 +51111,17 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -51145,13 +51145,13 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>1171.82</v>
+        <v>18445</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>3776-516-CM26</t>
+          <t>539119-3323-CM26</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -51176,17 +51176,17 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -51216,7 +51216,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>4121-82-CM26</t>
+          <t>1233616-1906-CM26</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -51241,12 +51241,12 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -51256,12 +51256,12 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
@@ -51275,13 +51275,13 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>1079.57</v>
+        <v>46131.54</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>1233616-1906-CM26</t>
+          <t>4121-82-CM26</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -51306,12 +51306,12 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -51321,12 +51321,12 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
@@ -51340,7 +51340,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>46131.54</v>
+        <v>1079.57</v>
       </c>
     </row>
     <row r="786">
@@ -51671,7 +51671,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>1230771-41-CM26</t>
+          <t>623663-205-CM26</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -51686,7 +51686,7 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -51696,12 +51696,12 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>65.080.277-2</t>
+          <t>65.030.848-4</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
+          <t>AGENCIA CHILENA DE EFICIENCIA ENERGETICA</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -51730,13 +51730,13 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>1774.05</v>
+        <v>19693.45</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>701-631-CM26</t>
+          <t>1230771-41-CM26</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -51761,27 +51761,27 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>65.080.277-2</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Desarrollo Social de la Municipalidad de Independencia</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K792" t="inlineStr">
@@ -51795,13 +51795,13 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>20230.48</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>4931-123-CM26</t>
+          <t>701-631-CM26</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -51816,7 +51816,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -51826,17 +51826,17 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>65.613.130-6</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -51860,7 +51860,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>1719.43</v>
+        <v>20230.48</v>
       </c>
     </row>
     <row r="794">
@@ -51926,6 +51926,136 @@
       </c>
       <c r="M794" s="2" t="n">
         <v>7481.38</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>4931-123-CM26</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>65.613.130-6</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M795" s="2" t="n">
+        <v>1719.43</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>717503-304-CM26</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>69.265.990-2</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>Asociación Chilena de Municipalidades</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M796" s="2" t="n">
+        <v>8255.860000000001</v>
       </c>
     </row>
   </sheetData>
